--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,8 +78,13 @@
       <color rgb="002D6A4F"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -181,6 +186,11 @@
         <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -208,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -283,6 +293,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -27730,7 +27746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -28514,6 +28530,487 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Glamnetic</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Press-On Nails / Lashes</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>She wears press-on nails. Glamnetic is a top creator-friendly nail brand. This is a direct personal fit.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Partnerships</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Influencers@glamnetic.com</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>@glamnetic</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Also: PR@glamnetic.com / Wholesale@glamnetic.com -- send to Influencers@ first</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>imPRESS by Revlon</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Press-On Nails</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Press-on nails. She wears them every day. imPRESS is mass-market and creator-forward.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Brand/Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>help@impressbeauty.com</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>@impressbeauty</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Also: orders@impressbeauty.com -- help@ is the better contact for brand inquiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Sunday II Sunday</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Natural hair care brand made for active Black women. She has natural hair. Values and audience align.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>@sundayiisunday</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Featured on Ulta's Black-owned/founded page. Find contact at sundayiisunday.com/pages/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BLK/OPL</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Black-Owned Beauty</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Black-owned cosmetics brand. Her audience is primarily Black women. Natural story fit.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>@blkopl</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Featured on Ulta's Black-owned/founded page</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Mented Cosmetics</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Black-Owned Beauty</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Black-owned brand focused on inclusive nudes for deeper skin tones. Strong community alignment.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>@mentedcosmetics</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Featured on Ulta's Black-owned/founded page. Founder is public-facing -- can pitch directly on IG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Juvia's Place</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Black-Owned Beauty</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Bold, vibrant makeup brand with a deeply loyal Black audience. Her community and theirs overlap.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>@juviasplace</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Featured on Ulta's Black-owned/founded page</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ulta Beauty</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Beauty Retail</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>She is their customer. Natural hair, press-on nails, Black woman -- she shops Ulta regularly.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Influencer/Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>@ultabeauty</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>MUSE Accelerator (MUSEAccelerator@ulta.com) is for Black-OWNED brands, not influencers. Pitch through their creator/affiliate program instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ASOS Curve</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ASOS has a dedicated plus-size line and works with micro/nano creators. She is a size 22/24.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>@asos</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>ASOS is known for working with smaller creators. ASOS Curve is the exact fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Glossier</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Clean Beauty</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Glossier works with micro creators and their 'you look like yourself' ethos fits her body positivity brand.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Creator Program</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>@glossier</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>They have a rep program. Apply at glossier.com or pitch directly via IG DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>The Ordinary</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Affordable, educational skincare. Her audience (women 25-54) is their core demographic.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Affiliate/Creator</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>@theordinary</t>
+        </is>
+      </c>
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>The Ordinary has a public affiliate/ambassador program. Good fit for educational skincare content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>OUAI</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Hair Care</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Lifestyle hair brand. Decent if she creates hair content -- less relevant if not a hair focus.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>@theouai</t>
+        </is>
+      </c>
+      <c r="G29" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Lower priority. Only pursue if she wants to lean into natural hair content more.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,8 +83,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -191,6 +196,11 @@
         <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -218,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -299,6 +309,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -27746,7 +27759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -29011,6 +29024,1027 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SoulAdorne</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Jewelry</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Fashion/lifestyle jewelry. Complements her style content -- she does kitten heels and fashion, accessories fit naturally.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Direct email</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>souladorne@outlook.com</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>@souladorne</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Direct email in hand. Send today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Glow Jewellery</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Jewelry</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Creator-friendly jewelry brand. Named contact (Lauren) available -- warm pitch.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Lauren (direct)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>lauren@glowjewellery.co</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>@glowjewellery</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Personal contact email. Mention her audience and style content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Alden + Mara</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Jewelry</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Ambassador program exists -- they are actively recruiting creators.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Ambassador Application</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>@aldenandmara</t>
+        </is>
+      </c>
+      <c r="G32" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>No direct email. Apply through Ambassador Application on their site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Louis G. Jewelry</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Jewelry</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Ambassador program exists.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Ambassador Application</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>@louisgjewelry</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>No direct email. Apply through their Ambassador Application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Snows Design</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Jewelry</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Ambassador program exists.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Ambassador Program</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>@snowsdesign</t>
+        </is>
+      </c>
+      <c r="G34" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>No direct email. Apply through their Ambassador Program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Eclaire Nail Studio</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Press-On Nails</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>She wears press-on nails daily. Direct creator-run nail brand with a personal email -- warm pitch.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Direct email</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>eclairenailstudios@gmail.com</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>@eclairenailstudio</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Direct email. Small brand = more flexibility, faster reply. Pitch personal and specific.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Olive &amp; June</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Nails</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>One of the most creator-forward nail brands in the market. Known for working with micro creators.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Partnerships</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>hello@oliveandjune.com</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>@oliveandjune</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Direct email. Strong brand with proven creator program. High priority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Mari by Marsai</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Press-On Nails</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Marsai Martin's nail brand -- Black-founded, culturally relevant, strong community overlap.</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Contact Form</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>@maribymarsai</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>No direct email. Contact via form on website. Worth the effort given the cultural fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Pear Nova</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Nails</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Black-owned nail brand. Nontoxic, inclusive. Aligns with her values and audience.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Contact Form</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>@pearnova</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>No direct email. Contact via form. Black-owned -- strong pitch angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Lilly Lashes</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Lashes</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Top-tier lash brand with an active creator program. She uses lashes -- direct personal fit.</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Direct email</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>hello@lillylashes.com</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>@lillylashes</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Direct email. One of the most recognized names in the lash space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>OLB Lashes</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Lashes</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Creator-friendly lash brand. Direct email available.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Direct email</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>INFO@OLBLASHES.COM</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>@olblashes</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Direct email. Pitch her as a regular lash wearer who can create authentic content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Lashify</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Lashes</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Lashify has a dedicated incubator program for creators. That email is SPECIFICALLY for partnership pitches.</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Incubator Program</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>incubator@lashify.com</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>@lashify</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>incubator@lashify.com is purpose-built for creator deals. This is the strongest contact in the lash category. Send soon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Naturalicious</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Natural hair care brand built for Black women. She has natural hair. Perfect values and product fit.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Concierge/Partnerships</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>concierge@naturalicious.net</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>@naturalicious</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Direct email. Natural hair creator content. Pitch around her hair journey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Eden BodyWorks</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Black-founded natural hair brand. 'Curlfriends' email signals they actively work with creators.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>curlfriends@edenbodyworks.com</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>@edenbodyworks</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>The email address 'curlfriends' is literally their creator/community contact. Strong signal they want partnerships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Northwest Scents</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Hair Care</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Natural hair care. Contact form only.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Contact Form</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Contact form only. Low priority unless she specifically likes this brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Tiimo</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>ADHD / Productivity App</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Visual daily planner designed for ADHD. If she uses it or relates to this, authentic content writes itself.</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Creator/Affiliate Program</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>@tiimo_app</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>ADHD niche is growing fast with creators. Tiimo actively works with ADHD creators. Pitch as someone who understands the lived experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Focus Bear</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ADHD / Productivity App</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>ADHD habit-tracking app. Small enough to be creator-friendly and move fast.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Creator Program</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>@focusbearapp</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Smaller app = faster deal, more flexibility. Good entry into the ADHD creator space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Brain.fm</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Focus / ADHD App</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Music for focus and ADHD. Simple pitch: 'I use this when I am deep in work.'</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Affiliate/Creator</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>@brainfm</t>
+        </is>
+      </c>
+      <c r="G47" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>They have a creator affiliate program. Lower-effort pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Goblin Tools</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>ADHD Tools</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>AI task-breaking tools popular with the ADHD community. Very niche but loyal audience.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Creator / Affiliate</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>@goblintools</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Newer, smaller product. Good for authentic ADHD content if she is open about it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Insight Timer</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Meditation / Wellness App</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Free meditation app with a large diverse community. Creator partnerships available.</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Affiliate/Creator</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>@insighttimer</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Large platform. Works with creators in the wellness and mindfulness space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Headspace</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Meditation / Mental Health App</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Top-tier meditation app. Creator program exists -- higher follower count typically preferred.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>@headspace</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>More selective than smaller apps. Worth pitching but may need more growth first. Revisit at 75K.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Calm</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Sleep / Mental Health App</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>One of the biggest mental health apps. Very active with influencer deals.</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>@calm</t>
+        </is>
+      </c>
+      <c r="G51" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Calm does big influencer deals. At 52K they may engage -- pitch the 4% engagement and community trust angle over raw follower count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>BetterHelp</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Online Therapy Platform</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Massive creator deal history. Her resilience and mental health advocacy are a natural match.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>@betterhelp</t>
+        </is>
+      </c>
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>FLAG: BetterHelp had controversy in 2022 over creator partnerships without proper therapy disclaimers. They have cleaned this up, but read their current creator terms carefully before signing anything. The pay is real -- just protect yourself.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -27759,7 +27759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -30045,6 +30045,2317 @@
         </is>
       </c>
     </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Kane's Furniture</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Florida/Home Lifestyle</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Florida's largest furniture chain. She lives in Orlando, is a millennial building her space. Local brand, local creator -- easy yes.</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Marketing / Local Partnerships</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>marketing@kanesfurniture.com</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>@kanesfurniturefl</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Florida-based, family-owned. They sponsor local events. Strong local creator angle. Pitch: Orlando creator, local following, home lifestyle content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>City Furniture</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Florida/Home Lifestyle</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>South Florida furniture chain with locations statewide. Millennial homeowner/renter content angle.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Director</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>@cityfurniture</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Sister brand to Ashley HomeStore. Florida-headquartered. Contact via cityfurniture.com/about/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Rooms To Go</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Home Lifestyle</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Tampa-headquartered furniture chain. Strong brand awareness in her market.</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>@roomstogo</t>
+        </is>
+      </c>
+      <c r="G55" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Rooms To Go HQ is in Seffner, FL. Local Florida angle is real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Florida/Lifestyle</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Publix is Florida-loyal. She shops there. They have a creator/community partnership history in FL.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Community Partnerships</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>@publix</t>
+        </is>
+      </c>
+      <c r="G56" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Publix does not do traditional influencer deals, but they sponsor local community events -- back-to-school event angle is strong here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Visit Orlando</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Florida Tourism</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>She IS Orlando. Local creator with 52K followers, 74% women -- they want this voice.</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Media &amp; Creator Relations</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>media@visitorlando.com</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>@visitorlando</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Visit Orlando actively recruits local and regional content creators. Pitch as the face of an authentic Orlando story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Visit Florida</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>State Tourism</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>State-level tourism board. She lives here and represents the state with national reach.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Creator/Media Partnerships</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>@visitflorida</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Visit Florida has a formal press/creator program. Find contact at visitflorida.org/media</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Rosen Hotels &amp; Resorts</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Florida Hospitality</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Orlando-based independent hotel group. Supports local community heavily -- she does community work.</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Marketing / PR</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>@rosenhotels</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>Local Orlando hotel chain. Community-oriented brand. Her back-to-school event and community work is the right angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Hard Rock Hotel Orlando</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Florida Hospitality</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Iconic brand. She was in a Romeo Santos music video -- music + culture crossover, this fits.</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>PR / Partnerships</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>@hardrockorlando</t>
+        </is>
+      </c>
+      <c r="G60" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Universal partner. Music and culture angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Loews Hotels</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Florida Hospitality</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Major Florida hotel chain, Universal partner. Experiential brand with a strong lifestyle angle.</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Marketing/Creator</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>@loewshotels</t>
+        </is>
+      </c>
+      <c r="G61" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>Multiple Orlando properties. Creator-friendly hospitality brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Universal Orlando Resort</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Florida Tourism</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>She is in Orlando. Content around theme parks is massive with her demographic.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Creator/Influencer Relations</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>influencer@universalorlando.com</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>@universalorlando</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Universal has an active local creator program. Her Orlando identity is the hook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Marriott Bonvoy</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Hotels / Travel</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Marriott has one of the most active influencer programs in hospitality. She has Hilton -- Marriott is the next door.</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>@marriottbonvoy</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>Apply at creator.marriott.com or pitch via partnerships@marriott.com. Already has Hilton credential to reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Hyatt Hotels</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Hotels / Travel</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Hyatt's World of Hyatt program works with lifestyle and travel creators. Her travel-for-speaking angle opens this door.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Brand &amp; Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>@worldofhyatt</t>
+        </is>
+      </c>
+      <c r="G64" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>She travels for speaking engagements. Travel content is a natural byproduct of her speaker life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Omni Hotels &amp; Resorts</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Hotels / Travel</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Upscale hotel brand that has done creator campaigns. Her Hilton credit is a direct comparable.</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Marketing / PR</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>@omnihotels</t>
+        </is>
+      </c>
+      <c r="G65" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>Hilton and Omni are comparable tiers. Existing hotel brand credit opens this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Cruise / Travel</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Miami-based. Her audience (Southern US, Orlando) is Carnival's core demo. She is literally in their backyard.</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Influencer Relations</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>influencer@carnival.com</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>@carnival</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Carnival is headquartered in Miami. Her Florida base is the hook. They have an active creator program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Royal Caribbean</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Cruise / Travel</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Miami-based, aspirational travel brand with a huge creator program.</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>@royalcaribbean</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>RCL HQ is in Miami. Strong creator program. Her Florida-based travel content angle works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Cruise / Travel</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Miami-based. Millennial-friendly, more casual than some cruise brands.</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>@norwegiancruiseline</t>
+        </is>
+      </c>
+      <c r="G68" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>NCL HQ is Miami. Similar pitch to Royal Caribbean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Southwest Airlines</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Orlando is one of Southwest's biggest markets. She flies for speaking gigs -- authentic travel content.</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Creator/Partnerships</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>@southwestair</t>
+        </is>
+      </c>
+      <c r="G69" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>Southwest has a Community Relations team and a Rapid Rewards ambassador program. Her speaking travel is authentic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>JetBlue</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>JetBlue's HQ is NYC but major Florida hub. Millennial travel brand, creator-friendly history.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>@jetblue</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>JetBlue has done notable creator campaigns. Florida is a key market for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>FabFitFun</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Subscription Box / Lifestyle</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Millennial women subscription box. 52K followers, 74% women, ages 25-54 -- she IS FabFitFun's audience.</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Partnerships</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>influencer@fabfitfun.com</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>@fabfitfun</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>FabFitFun does massive influencer campaigns. Her audience demo is exactly theirs. Send this week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Ipsy</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Beauty Subscription</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Beauty subscription box targeting millennial women. Plus-size inclusive brand partnerships.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Creator Program</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>creator@ipsy.com</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>@ipsy</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Ipsy has a large creator network. Direct email known. Strong fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Stitch Fix</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Fashion / Styling</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Personal styling subscription with a plus-size offering (Stitch Fix Plus). She's a size 22/24.</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>@stitchfix</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>Pitch the Stitch Fix Plus angle. She gets styled boxes delivered -- authentic content opportunity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Rent the Runway</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Fashion / Lifestyle</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Designer rental for everyday wear and events. She does theater, events, speaking -- clothing variety is real.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>@renttherunway</t>
+        </is>
+      </c>
+      <c r="G74" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>RTR has a plus-size inventory. Her event/speaking lifestyle is an authentic use case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>ThredUp</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Sustainable Fashion</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Secondhand fashion platform. Millennial sustainability angle. They work with plus-size creators.</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>@thredup</t>
+        </is>
+      </c>
+      <c r="G75" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>ThredUp's Clean Out Kit + styling content is popular with millennial creators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Poppi</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Prebiotic Soda / Beverage</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Viral millennial-loved soda brand. Her late-July Florida event is a natural product fit.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>@drinkpoppi</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Poppi does heavy influencer campaigns. Lemonade/beverage angle for late-July event. Send this month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>OLIPOP</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Functional Soda</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Functional soda brand with a huge creator program. Millennial wellness audience overlap.</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>@drinkolipop</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>OLIPOP is aggressively expanding creator deals. Her wellness/body positive platform aligns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Hydration / Wellness</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Hydration brand targeting active millennials. She travels for speaking -- hydration on the road is authentic.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Influencer Partnerships</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>@liquidiv</t>
+        </is>
+      </c>
+      <c r="G78" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Liquid I.V. has a large creator program. Active lifestyle + travel = natural content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Athletic Brewing</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Non-Alcoholic Beverage</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Non-alcoholic beer brand popular with health-conscious millennials. Wellness angle, event angle.</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>@athleticbrewing</t>
+        </is>
+      </c>
+      <c r="G79" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>Events, Florida summer, staying clear-headed -- authentic content possibilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Design Tool / Creative</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Canva works with creators who use their product for content. She already uses Canva.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Creator/Education Program</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>@canva</t>
+        </is>
+      </c>
+      <c r="G80" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Canva Education and Creator programs exist. She makes media kits, graphics -- authentic user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Bumble</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Dating / Social App</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Bumble does massive creator campaigns. Bumble BFF and networking editions go beyond dating -- she builds community.</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Ambassador Program</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>ambassadors@bumble.com</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>@bumble</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>Bumble pays well and their campaigns focus on women's empowerment -- exact alignment. Also: Bumble BFF is a real fit for her community-building message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Hinge</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Dating App</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Millennial dating app. Single women creator angle, authentic lifestyle content.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Partnerships</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>@hinge</t>
+        </is>
+      </c>
+      <c r="G82" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Hinge has done creator campaigns. Less obvious fit than Bumble but worth pitching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Solo Stove</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Outdoor Lifestyle</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Lifestyle brand targeting independent, experience-focused millennials. She does events.</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>@solostove</t>
+        </is>
+      </c>
+      <c r="G83" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>More of a stretch -- only pursue if she creates outdoor/gathering content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Turo</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Peer-to-Peer Car Rental</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Millennial-friendly car rental alternative. She travels for speaking and events.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Creator Program</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>@turo</t>
+        </is>
+      </c>
+      <c r="G84" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Turo has a creator program. Florida-based road trips, travel-for-speaking content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="42" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Knix</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Inclusive Intimates</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Body-positive inclusive underwear and intimates brand. Made for every body. Perfect alignment.</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>@knixwear</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>Knix is explicitly body-positive and runs extensive creator campaigns. Strong values match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Thinx</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Period Underwear</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Inclusive period care brand. Her body image advocacy and women's health positioning aligns.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>@thinx</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Thinx does creator campaigns. Women's health + body acceptance angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Cora</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Period Care</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Organic period care brand targeting women 25-40. Her audience is exact demo.</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>@corawomen</t>
+        </is>
+      </c>
+      <c r="G87" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>Clean period care brand with a strong millennial following.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Spanx</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Shapewear</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>YITTY is Lizzo's competitor to Spanx. She already works in this space. Spanx is the legacy.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>@spanx</t>
+        </is>
+      </c>
+      <c r="G88" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>She is already in YITTY/Fabletics. Spanx partnership would require checking exclusivity. Note that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="42" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Food Delivery</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>DoorDash does creator campaigns. Her millennial lifestyle, Orlando base, and food content angle.</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Creator Marketing</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>@doordash</t>
+        </is>
+      </c>
+      <c r="G89" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>DoorDash runs seasonal creator campaigns. Easy lifestyle integration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Uber Eats</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Food Delivery</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Millennial-targeted delivery app. Creator campaigns frequent.</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>@ubereats</t>
+        </is>
+      </c>
+      <c r="G90" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Competing with DoorDash -- pitch one at a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>HelloFresh</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Meal Kit Delivery</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Millennial meal kit brand. Home cooking content, independence angle, millennial lifestyle.</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Partnerships</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>influencer@hellofresh.com</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>@hellofresh</t>
+        </is>
+      </c>
+      <c r="G91" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>HelloFresh has a large influencer program. Direct email known.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Universal Standard</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Size-inclusive fashion brand (00-40). Well-made clothes for every body. Her audience is their audience.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>@universalstandard</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Premium plus-size brand. Strong values alignment. She wears 22/24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Savage X Fenty</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Inclusive Lingerie</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Rihanna's inclusive lingerie brand. Her audience and aesthetic overlap heavily.</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Influencer/Creator</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>@savagexfenty</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>Body positive, size-inclusive, Black-founded adjacent culture. Strong fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Girlfriend Collective</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Inclusive Activewear</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Size-inclusive sustainable activewear. Body positive, millennial-targeted, creator-friendly.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>@girlfriend</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Girlfriend Collective actively recruits diverse creators. XS-6XL range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>11 Honoré</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Plus-Size Luxury Fashion</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Designer plus-size fashion platform. She has Vogue credits. Luxury fashion is her caliber.</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Brand/Creator</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>@11honore</t>
+        </is>
+      </c>
+      <c r="G95" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>High-end plus-size. Her Vogue editorial and media presence positions her for this tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Dia &amp; Co</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Plus-Size Subscription Box</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Styling subscription specifically for plus-size women. She IS their customer.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>@diandco</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Direct product fit. She gets clothes she'd actually wear -- authentic content opportunity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="42" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Ritual</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Women's Vitamins</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Clean vitamins brand targeting millennial women. Transparent ingredients, women's health focus.</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>@ritual</t>
+        </is>
+      </c>
+      <c r="G97" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>Ritual has a large creator program. Women's health + self-care angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="42" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Hims &amp; Hers</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Telehealth / Wellness</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Hers (women's side) covers mental health, skin, hair -- her audience is exactly Hers' target.</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>@forhers</t>
+        </is>
+      </c>
+      <c r="G98" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Hers has mental health and body care products. Creator program exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Curology</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Custom skincare subscription. Millennial women 25-40. Her audience is their audience.</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>@curology</t>
+        </is>
+      </c>
+      <c r="G99" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>Large influencer program. Authentic skincare content opportunity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Audio / Music</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>She has appeared on NPR and is a public speaker. Podcast and audio content is natural for her.</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Creator Program</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>@spotify</t>
+        </is>
+      </c>
+      <c r="G100" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Spotify for Podcasters and Spotify Creator programs exist. Her voice + storytelling background is the pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="42" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>SiriusXM</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Radio / Audio</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>She has radio credits (NPR 2024). SiriusXM works with cultural voices.</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Media/Creator</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>@siriusxm</t>
+        </is>
+      </c>
+      <c r="G101" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>Her NPR credit is a credential here. Pitch as a cultural voice, not just a creator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Cash App</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Fintech / Banking</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Cash App does massive creator campaigns targeting Black millennials. Her audience is their audience.</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Creator Marketing</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>@cashapp</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Cash App is one of the biggest spenders in Black creator marketing. Her audience is exactly theirs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Fintech / Banking</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>No-fee banking app popular with millennials. Creator campaigns are frequent.</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>@chime</t>
+        </is>
+      </c>
+      <c r="G103" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>Chime targets unbanked/underbanked communities and does heavy creator marketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Eventbrite</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Events Platform</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>She runs community events -- back-to-school, lemonade event. Eventbrite could sponsor or co-brand.</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Creator/Community Partnerships</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>@eventbrite</t>
+        </is>
+      </c>
+      <c r="G104" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Pitch as a community event organizer, not just an influencer. She has a track record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Etsy</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Creator / Handmade Marketplace</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Etsy targets creative, independent millennial women. Creator/seller culture overlap.</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Creator Program</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>@etsy</t>
+        </is>
+      </c>
+      <c r="G105" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>Lower priority but Etsy has influencer partnerships around creator economy content.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -27759,7 +27759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -32356,6 +32356,2594 @@
         </is>
       </c>
     </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Sun Bum</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Sun Care / Beach Lifestyle</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Florida brand born in Cocoa Beach. She lives in FL. Local brand love + summer event sponsorship angle.</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Marketing / Creator</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>@sunbumproducts</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Sun Bum is Cocoa Beach, FL founded. Perfect Florida story. Lemonade event sun care sponsor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Coppertone</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Sun Care</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Major sun care brand. Back-to-school and summer events are exact partnership hooks.</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Brand / Influencer</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>@coppertone</t>
+        </is>
+      </c>
+      <c r="G107" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>Summer Florida event sponsor angle. Back-to-school outdoor event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Banana Boat</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Sun Care</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Mass market sun care, large creator program, Florida summer is their whole brand.</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>@bananaboatusa</t>
+        </is>
+      </c>
+      <c r="G108" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Summer outdoor event, back-to-school outdoor angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>EltaMD</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Premium Sun Care</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Premium skincare-forward sunscreen. Her audience is women 25-54 who care about skin health.</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Creator/Medical Partnerships</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>@eltamd</t>
+        </is>
+      </c>
+      <c r="G109" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>She co-created Institute for Body Image with medical professionals -- premium sunscreen has a wellness angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Hydro Flask</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Water Bottle / Outdoor</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Millennial lifestyle water bottle brand with a huge creator program.</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Ambassador / Creator</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>@hydroflask</t>
+        </is>
+      </c>
+      <c r="G110" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Summer outdoor event, hydration, Florida lifestyle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Stanley</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Tumbler / Lifestyle</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Stanley cups are a cultural moment with millennial women. Perfect for lemonade event content.</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>@stanleypmg</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>A Stanley x lemonade event collab is practically a meme at this point -- and that is why it works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>YETI</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Outdoor / Cooler</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Premium outdoor brand. Late-July Florida event needs coolers. Authentic product placement angle.</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>@yeti</t>
+        </is>
+      </c>
+      <c r="G112" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Event sponsor for lemonade/outdoor event. YETI coolers at a summer gathering = natural content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Simple Modern</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Drinkware / Lifestyle</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Affordable alternative to Stanley. Very creator-forward, plus-size inclusive marketing history.</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>influencer@simplemodern.com</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>@simplemodern</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>Simple Modern actively recruits mid-size creators. Direct email found. Summer event angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Kia</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Kia targets younger, diverse millennials. She travels for speaking. Content opportunity is road-trip / speaking tour.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Brand / Creator</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>@kia</t>
+        </is>
+      </c>
+      <c r="G114" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Kia's brand refresh targets millennials of color. Her speaking travel is authentic car content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Toyota's multicultural marketing is well-funded. She's in their demo and lifestyle.</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Multicultural Marketing</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>@toyota</t>
+        </is>
+      </c>
+      <c r="G115" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>Toyota has a dedicated multicultural marketing team. Her audience is exactly their target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Hyundai targets millennial women with lifestyle-forward campaigns.</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>@hyundaiusa</t>
+        </is>
+      </c>
+      <c r="G116" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Hyundai has done creator campaigns with lifestyle and culture-focused women creators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Volkswagen</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>VW is millennial-friendly, design-forward. Less saturated with Black creators than Toyota/Kia.</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Creator / Brand</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>@vw</t>
+        </is>
+      </c>
+      <c r="G117" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>Lower priority but less competitive than other car brands for her audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Turo</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Peer Car Sharing</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Millennial-targeted car rental alternative. She travels often, this is an authentic product.</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Creator Program</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>@turo</t>
+        </is>
+      </c>
+      <c r="G118" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Already in tracker -- verify not duplicate. Turo is worth pitching twice if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Enterprise Rent-A-Car</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Car Rental</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Florida has massive Enterprise presence. She has Sixt cred -- car rental partnerships are her lane.</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Marketing / Partnerships</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>@enterpriserentacar</t>
+        </is>
+      </c>
+      <c r="G119" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>Her Sixt national commercial is a direct credential for car brand pitches. Enterprise is everywhere in FL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Peacock</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Streaming</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>NBC's streaming platform. She has national TV credits. Content creator / on-camera angle.</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Creator / Talent</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>@peacocktv</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Her TLC, Jennifer Hudson Show, Tamron Hall credits all live on NBC/streaming universe. Natural pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Hulu</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Streaming</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Hulu has done creator campaigns with cultural voices. Her actress + influencer combo is the pitch.</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>@hulu</t>
+        </is>
+      </c>
+      <c r="G121" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>Hulu targets millennials and diverse audiences heavily.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Prime Video</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Streaming</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Prime has a creator program and auditions Black on-camera talent regularly.</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Creator / Talent Relations</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>@primevideo</t>
+        </is>
+      </c>
+      <c r="G122" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Her actress credits make this a dual pitch -- content creator AND talent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Tubi</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Streaming</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Free streaming platform targeting multicultural millennials. Less competitive than Netflix/Hulu.</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Creator / Brand</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>@tubi</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>Tubi's audience is Black millennials. She is Black, millennial, on-camera talent. Fast yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>BET+</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Streaming</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>BET is already in her world -- she was at BET Beauty Brunch as Host. This is a natural extension.</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Creator / Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>@betplus</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>She HAS ALREADY HOSTED a BET event. This is a warm pitch, not cold outreach. Lead with that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>OWN (Oprah Winfrey Network)</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>TV / Streaming</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>OWN targets Black women 25-54. Her audience is OWN's audience. Body image + resilience is their content.</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Brand / Creator</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>@owntv</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>OWN's audience is literally 'Danni Adams fans who haven't found her yet.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Home Cleaning</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Clean, design-forward cleaning brand. Millennial households. Creator campaigns exist.</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Brand / Influencer</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>@methodhome</t>
+        </is>
+      </c>
+      <c r="G126" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Method works with lifestyle and home content creators. Millennial household angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Mrs. Meyer's</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Home Cleaning</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Values-aligned cleaning brand. Natural products, garden scents -- her home content angle.</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>@mrsmeyersclean</t>
+        </is>
+      </c>
+      <c r="G127" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>Mrs. Meyer's has done creator campaigns. Natural, feel-good home products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Grove Collaborative</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Sustainable Home</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Sustainable home and cleaning brand. Millennial values, subscription model.</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>@grovecollaborative</t>
+        </is>
+      </c>
+      <c r="G128" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Grove works with millennial women creators on sustainable living content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Febreze</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Home / Lifestyle</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;G brand with mass-market creator programs. Easy lifestyle integration.</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>@febreze</t>
+        </is>
+      </c>
+      <c r="G129" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>Lower priority but P&amp;G brands run constant creator campaigns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>OXO</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Kitchen / Home</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Design-forward kitchen and home tools. Millennial home brand.</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Creator / Ambassador</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>@oxo</t>
+        </is>
+      </c>
+      <c r="G130" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>OXO works with lifestyle and home creators. Entry-level brand deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>MasterClass</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Online Education</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Premium creator-educator platform. She IS the type of person MasterClass features.</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Creator / Partnerships</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>partnerships@masterclass.com</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>@masterclass</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>MasterClass features people with lived expertise. Her Harvard speaker + Institute for Body Image credentials are exactly the MasterClass profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn Learning</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>She speaks on career building without an agent -- LinkedIn's audience is her message.</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Creator / Brand</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>@linkedin</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Her 'Nobody Is Coming to Save You' talk is a LinkedIn article waiting to happen. Creator partnerships here are real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Skillshare</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Online Education</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Creator education platform. She teaches social media and storytelling workshops.</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Creator Program</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>@skillshare</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>She runs workshops. Skillshare is literally a platform for her workshop content. Natural deal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Udemy</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Online Education</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Millennial professional development platform with creator courses.</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Instructor / Creator</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>@udemy</t>
+        </is>
+      </c>
+      <c r="G134" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Her social media and storytelling workshops could live on Udemy as a course.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>Coursera</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Online Education</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>University-backed learning. She has Harvard and university speaking cred -- this is aligned.</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Creator / Brand</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>@coursera</t>
+        </is>
+      </c>
+      <c r="G135" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>Long play. Credibility angle more than product angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Tijuana Flats</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Florida Restaurant Chain</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Florida-based Tex-Mex chain. Local brand, community-minded. She is in Orlando.</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Marketing / Local</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>@tijuanaflats</t>
+        </is>
+      </c>
+      <c r="G136" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Local Florida chain. Community partnership angle, back-to-school or lemonade event co-sponsor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Wawa</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Florida Convenience</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Wawa has expanded heavily into Florida and builds community loyalty. Millennial-loved brand.</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Marketing / Community</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>@wawa</t>
+        </is>
+      </c>
+      <c r="G137" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>Wawa does community sponsorships in FL. Her community events angle is the pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="42" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Smoothie King</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Health / Beverage</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>National smoothie chain heavy in the South. Summer Florida event sponsor.</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Marketing / Influencer</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>@smoothieking</t>
+        </is>
+      </c>
+      <c r="G138" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Summer event, health and wellness, Florida presence. Easy product integration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="42" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>Tropical Smoothie Cafe</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Florida / Beverage</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Florida-born smoothie brand. Summer event sponsor, local feel.</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Brand / Marketing</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>@tropicalsmoothiecafe</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>Florida brand, summer event, health-forward. Her lemonade event could co-brand with a smoothie chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="42" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Chick-fil-A</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Chick-fil-A does heavy community marketing in the South. Back-to-school event angle is real.</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Community Marketing</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>@chickfila</t>
+        </is>
+      </c>
+      <c r="G140" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Back-to-school event. Chick-fil-A does local community event sponsorships in the South.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="42" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Acorns</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Micro-Investing App</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Millennial-targeted investing app. Her 'nobody is coming to save you' financial independence message aligns.</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>@acorns</t>
+        </is>
+      </c>
+      <c r="G141" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>Financial empowerment + millennial women = Acorns' audience. Her independence message is on-brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="42" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Fintech / Banking</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Millennial financial services brand with a large creator program.</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Brand / Influencer</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>@sofi</t>
+        </is>
+      </c>
+      <c r="G142" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>SoFi targets millennial professionals. Her speaker/entrepreneur identity is their customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="42" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Lemonade Insurance</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Insurance / Fintech</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>The fact that it is LITERALLY called Lemonade is not lost on me. Millennial insurance brand.</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>@lemonade_inc</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>Her lemonade event + Lemonade Insurance is a pitch that writes itself. 'Life gives you lemons, your insurance should not.' Send this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="42" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Root Insurance</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Insurance / Fintech</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Millennial-targeted car insurance brand with active creator deals.</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>@joinroot</t>
+        </is>
+      </c>
+      <c r="G144" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>She drives for speaking gigs. Car insurance for independent millennial women is the angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="42" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Fenty Beauty</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Beauty / Inclusive</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Rihanna's makeup brand built for every skin tone. Her audience is Fenty's audience.</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>@fentybeauty</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>Fenty's core audience is Black women who prioritize inclusive shade ranges. She IS the customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="42" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Pat McGrath Labs</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Beauty / Luxury</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Pat McGrath is Black-founded luxury makeup. Her Vogue credit positions her for luxury beauty.</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Brand / PR</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>@patmcgrathreal</t>
+        </is>
+      </c>
+      <c r="G146" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Her Vogue editorial and luxury brand history (Hilton, Sixt) positions her for premium beauty pitches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="42" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Fenty Skin</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Rihanna's inclusive skincare line. Same audience as Fenty Beauty.</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>@fentyskin</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>Natural extension of Fenty Beauty pitch -- pitch both together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>e.l.f. Cosmetics</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Beauty / Accessible</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>e.l.f. is known for micro-creator deals and is very accessible price point. Her audience buys this brand.</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Influencer Partnerships</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>@elfcosmetics</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>e.l.f. runs constant micro and mid-tier creator campaigns. Her 4% engagement is their dream metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>NYX Cosmetics</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Beauty</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>L'Oreal-owned brand known for working with diverse creators. Bold makeup, accessible price.</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>@nyxcosmetics</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>NYX has a strong Black creator history. Bold, expressive looks align with her brand energy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="42" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>NARS</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Luxury Beauty</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Premium makeup brand. Her media credits (Vogue, national TV) position her for premium beauty.</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>PR / Creator</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>@narsissist</t>
+        </is>
+      </c>
+      <c r="G150" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>NARS does creator campaigns. Her editorial credits make this a realistic pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="42" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>Charlotte Tilbury</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Luxury Beauty</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Celebrity-loved makeup brand. Her TV and editorial background is the credential.</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>PR / Influencer</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>@charlottetilbury</t>
+        </is>
+      </c>
+      <c r="G151" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>Premium brand. Her media credits and Hilton/Sixt partnerships establish her at this tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="42" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Sol de Janeiro</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Body Care / Fragrance</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Massively viral body care brand. Brazilian inspired, summer vibes, inclusive. Her Florida summer life.</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>@soldejaneiro</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Sol de Janeiro is having a massive cultural moment. Florida + summer + her audience = natural fit. Pitch now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="42" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Vacation Inc.</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Sunscreen / Lifestyle</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Nostalgia sunscreen brand born in Miami. Florida-native brand, viral with millennials.</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>@vacation</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>Miami-born sunscreen brand. Florida, summer, nostalgia, millennials -- she fits every box.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="42" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Natural Deodorant / Body</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Natural deodorant brand popular with health-conscious millennial women. Creator program active.</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>@nativecos</t>
+        </is>
+      </c>
+      <c r="G154" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Native runs consistent creator campaigns. Natural, clean body care -- her wellness angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Beekman 1802</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Goat Milk Skincare</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>QVC/HSN-beloved goat milk skincare brand with a devoted millennial following and creator program.</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Creator / Ambassador</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>@beekman1802</t>
+        </is>
+      </c>
+      <c r="G155" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>Beekman 1802 actively recruits mid-tier creators. Their audience overlaps with hers significantly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Old Navy</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Fashion / Inclusive</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Old Navy runs inclusive sizing up to 4X and does creator campaigns with diverse women.</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Brand / Influencer</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>@oldnavy</t>
+        </is>
+      </c>
+      <c r="G156" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Old Navy Navyist program and creator deals. Inclusive sizing, accessible price, her audience shops here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>H&amp;M</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Fashion / Accessible</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>H&amp;M has plus sizes and does creator campaigns. Accessible fashion for millennial women.</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>@hm</t>
+        </is>
+      </c>
+      <c r="G157" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>Lower priority but H&amp;M does constant creator activations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Fashion / Retail</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Nordstrom has an influencer program and features plus-size fashion. Her editorial cred positions her here.</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Creator / Ambassador</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>@nordstrom</t>
+        </is>
+      </c>
+      <c r="G158" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Nordstrom Trunk Club and their creator program. Her Vogue credit opens this door.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Rebdolls</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>Black-owned plus-size fashion brand. Direct community fit.</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Brand / Creator</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>@rebdolls</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>Black-owned plus-size brand. Her audience buys this. Her size 22/24 is their model size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Stewart</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Iconic plus-size fashion brand targeting Black women. She IS their customer.</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Brand / Influencer</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>@ashleystewart</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Stewart is THE plus-size brand for Black women. This should have been on the list from day one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>Steve Madden</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>Wide range of styles including kitten heels she prefers. Mid-tier, creator program exists.</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>Brand / Influencer</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr"/>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>@stevemadden</t>
+        </is>
+      </c>
+      <c r="G161" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>Steve Madden does creator campaigns. Kitten heels and statement shoes align with her style.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Nine West</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Classic women's shoe brand with a plus-friendly approach. Kitten heels are their signature.</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Creator / Partnerships</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>@ninewest</t>
+        </is>
+      </c>
+      <c r="G162" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Kitten heels + classic styles. Her fashion content angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Sneakers</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>New Balance has become a cultural moment with millennials and does creator campaigns.</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Brand / Creator</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr"/>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>@newbalance</t>
+        </is>
+      </c>
+      <c r="G163" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>New Balance has leaned into culture and diverse creators. Her sneaker preference and lifestyle fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>HOKA</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Running / Lifestyle Sneakers</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>HOKA targets active, comfort-seeking women. She wears sneakers, travels frequently.</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>@hoka</t>
+        </is>
+      </c>
+      <c r="G164" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>HOKA is everywhere right now with millennial women. Comfort + style is her footwear brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="42" customHeight="1">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Skechers</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Comfort / Lifestyle</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Comfort sneakers, wide sizing. Creator program active. Her preference for comfort shoes aligns.</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>Brand / Influencer</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr"/>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>@skechers</t>
+        </is>
+      </c>
+      <c r="G165" s="26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>Skechers does creator campaigns and has wide-width options. Comfort creator content.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Press Contacts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Email Tracker" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Brand Targets" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Podcast Targets" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,8 +89,12 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -201,6 +206,18 @@
         <fgColor rgb="00DDDDDD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A1A2E"/>
+        <bgColor rgb="001A1A2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4FF"/>
+        <bgColor rgb="00F0F4FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -228,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -314,6 +331,10 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -27759,7 +27780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -34944,6 +34965,3848 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Chocolate Kingdom</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Orlando / Experiential</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Bean-to-bar chocolate factory tour on I-Drive -- hands-on, visual, photogenic. Perfect 'only in Orlando' content.</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Marketing Manager / Owner</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>@chocolatekingdom</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>chocolatekingdom.com -- small enough to go direct to owner for gifted collab</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Waldorf Astoria Orlando</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Luxury Hotel / Dining</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Luxury hotel inside Disney Bonnet Creek with Bull &amp; Bear (OpenTable Top 100). Hilton brand -- she already has Hilton relationship to reference.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Director of Marketing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>@waldorfastoriaorlando</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>waldorfastoriaorlando.com -- complex marketing structure shared with Signia Hilton Bonnet Creek</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Medieval Times (Kissimmee)</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Orlando / Entertainment</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Dinner theater show near Orlando. Hosting/event sponsorship angle + 'girls' night out' content.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Director of Marketing</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>@medievaltimes</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>4510 W. Vine St., Kissimmee -- medievaltimes.com/orlando</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Pirates Dinner Adventure</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Orlando / Entertainment</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Immersive dinner show with 300,000-gallon indoor lagoon. Family and date night content angle.</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>@piratesdinneradventure</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>piratesdinneradventure.com -- 6400 Carrier Dr, Orlando</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>The Escape Game Orlando</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Orlando / Experiential</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Top-tier escape room on I-Drive. High-engagement 'challenge' content format -- group experience, great for brand collab day.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>@theescapegame</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>theescapegame.com/orlando</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Dave &amp; Buster's Orlando</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Orlando / Entertainment</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Arcade + sports bar + dining on I-Drive. Active influencer program at national and local level.</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Marketing Manager / Local GM</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>@daveandbusters</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>8986 International Dr -- national brand with local activation budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Ripley's Believe It or Not! Orlando</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Orlando / Experiential</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>16 galleries, iconic I-Drive landmark. 'I can't believe this is real' reaction content -- high shareability.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Marketing Manager / PR Manager</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>@ripleys</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>ripleys.com -- 8201 International Dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ICON Park Orlando</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Orlando / Entertainment Complex</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>20-acre open-air complex (The Wheel, Sugar Factory, SEA LIFE, Madame Tussauds, Blue Man Group). Named contact: Lorena Duarte, Sr. Director Corporate Sponsorships. Active partnerships page.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Lorena Duarte, Sr. Director Corporate Sponsorships</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>@iconparkorlando</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>iconparkorlando.com/strategic-partnerships-2 -- multiple venues under one umbrella</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Sugar Factory Orlando</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Orlando / Restaurant</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Candy wall, giant cocktails, most influencer-friendly restaurant on I-Drive. Gifted meal + content is standard for this brand.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Marketing Manager / Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>@sugarfactoryorlando_</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>sf3.sugarfactory.com/orlando-fl -- inside ICON Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Mister Car Wash</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>National / Florida Lifestyle</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>6+ Orlando locations. Unlimited Wash Club = natural gifted product. 'Treat yourself' self-care content angle. NYSE: MCW.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Director of Marketing (corporate)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>@mistercarwash</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>mistercarwash.com -- corporate HQ Tucson; regional marketing contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SunRail</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Orlando / Transit / Community</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Orlando commuter rail -- marketing budget active during FDOT transition. 'Explore Orlando by rail' content series angle.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Marketing Manager / Community Outreach</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>@sunrailorlando</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>corporate.sunrail.com -- info@sunrail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Brightline</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Florida / Travel / Rail</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Florida high-speed rail (Orlando, Miami, Fort Lauderdale). Day trip travel content. Inc. 2026 Fastest Growing. Actively seeking brand partnerships.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Director of Marketing Partnerships</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>@gobrightline</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>gobrightline.com/press-room -- aggressive partnership expansion 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>World Food Trucks</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Kissimmee / Food / Culture</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Largest food truck park in the US (100+ trucks), Kissimmee. Cultural food diversity angle, '100 trucks which is best?' content format.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Marketing Manager / Owner</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>@worldfoodtrucks</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>worldfoodtrucks.com -- 5811 W Irlo Bronson Memorial Hwy, Kissimmee</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Fun Spot America</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Orlando / Amusement</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Family-owned local amusement park (Orlando + Kissimmee). 'Support local vs big theme parks' content angle. #FindYourFun campaign.</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Marketing Director / Sponsorship Manager</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>@funspotamerica</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>fun-spot.com -- family-owned, decision-maker accessible</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>The View at Clermont National</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Clermont FL / Restaurant/Venue</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Restaurant + Toptracer driving range + panoramic views (Bella Collina, Lake Apopka, Disney). Dog-friendly, live music. High visual content value.</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Events Manager / Marketing Manager</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>@theviewclermont</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>viewclermont.com -- 2601 Clermont National Dr, Clermont FL</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Travel + Leisure Co.</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Orlando / Media / Travel Brand</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Opened global HQ in Downtown Orlando Jan 2026 (183K sq ft, 900+ employees). Explicitly seeking local Orlando business partnerships. Press + brand angle.</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>VP Communications / Director Community Partnerships</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>@travelandleisure</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>501 W. Church St., Downtown Orlando -- travelandleisureco.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Gaylord Palms Resort (ICE!)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Kissimmee / Holiday Event</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Annual ICE! holiday experience at Gaylord Palms -- top non-Disney holiday event in metro Orlando. Nov-Jan season. Active influencer program.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PR &amp; Partnerships Manager</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>@gaylordpalms</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>christmasatgaylordpalms.com -- 6000 W Osceola Pkwy, Kissimmee</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CurlMix</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Black-owned, clean curl products for 3A-4B. She has natural hair -- authentic fit.</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Brand Partnerships / Influencer Relations</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>@curlmix</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>curlmix.com -- Black-owned Chicago brand, Ulta</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Bread Beauty Supply</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Gentle milky cleanser for textured hair. Sephora/Ulta -- accessible, modern packaging.</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>@breadbeautysupply</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>breadbeautysupply.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Pattern Beauty</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Founded by Tracee Ellis Ross. 3B-4C focus. Wash Day kits, huge cultural cachet.</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Brand Partnerships / Influencer Relations</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>@patternbeauty</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>patternbeauty.com -- Ulta, Sephora, Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Cecred</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Beyonce's hair care line, sold at Ulta. Natural/textured hair. Major cultural moment.</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Brand Partnerships / PR</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>@cecred</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>cecred.com -- Ulta</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Camille Rose</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Black woman-owned (Janell Stephens, Atlanta). In 300K+ stores. Deep community credibility.</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>@camillerosenaturals</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>camillerosenaturals.com -- Ulta, Target, Walmart</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Adwoa Beauty</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Non-toxic, gender-neutral haircare for textured hair. Sephora. Clean beauty angle.</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>@adwoabeauty</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>adwoabeauty.com -- Sephora</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Briogeo</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Sulfate-free, cruelty-free. Popular conditioning masks. She has natural hair -- direct authentic use.</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Brand Partnerships / Influencer</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>@briogeohair</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>briogeohair.com -- Ulta, Sephora</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Big Bud Press</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>LA-based ethically made unisex basics, XXS-4XL. Body-positive brand ethos matches her advocacy work.</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>@bigbudpress</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>bigbudpress.com -- LA based, ships nationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Wildfang</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Inclusive Fashion</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>LGBT-owned brand with inclusive sizing to 3X/24. Values alignment + LA/national brand.</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Brand Partnerships</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>@wildfang</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>wildfang.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Little Words Project</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Jewelry / Accessories</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Beaded bracelets -- frequently runs gifting campaigns with micro/nano creators. No major barrier to entry.</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Influencer Relations</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>@littlewordsproject</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>littlewordsproject.com -- actively seeks nano/micro gifting</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>MIX:BAR</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Hair Accessories / Fragrance</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Sends PR gifts to nano influencers. Hair accessories + fragrance line.</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>PR / Influencer Relations</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>@mixbar</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>mixbar.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Princess Polly</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Fashion / Accessories</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Frequently emails nano creators for PR collabs. Accessible entry point.</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Influencer / PR Relations</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>@princesspolly</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>princesspolly.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>KISS / imPRESS</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Nails / Lashes</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Market leader in press-on nails. Walgreens/Walmart distribution. Mass market, active creator programs.</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Influencer Marketing</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>@impressbeauty</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>kissusa.com / impressbeauty.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Red Aspen</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Nails / Lashes / Beauty</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Social selling brand: press-on nails, lashes, skincare. Active creator program.</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Brand Ambassador / Influencer</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>@redaspennails</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>redaspenlove.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Erin Condren</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Stationery / Planning</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Major planner brand with ambassador program. Productivity + self-organization content angle.</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Ambassador Program Manager</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>@erincondren</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>erincondren.com -- active ambassador program</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Eola Food Hall</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Orlando / Food Hall</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>New 2-story, 15K sq ft food hall Downtown Orlando. 10 vendors + fine dining + wine room + Lake Eola views. Opening 2026.</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Marketing Manager / Owner</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Near Orlando Public Library -- new opening, great 'discover local' content</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Level 99 Orlando</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Orlando / Social Gaming</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Adult social gaming venue with 50+ physical/mental challenges, Night Shift Kitchen craft cocktails.</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>@level99ent</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>level99.com -- new opening Orlando</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Podcast Name</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="inlineStr">
+        <is>
+          <t>Host(s)</t>
+        </is>
+      </c>
+      <c r="C1" s="29" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="inlineStr">
+        <is>
+          <t>Audience Size</t>
+        </is>
+      </c>
+      <c r="E1" s="29" t="inlineStr">
+        <is>
+          <t>Based In</t>
+        </is>
+      </c>
+      <c r="F1" s="29" t="inlineStr">
+        <is>
+          <t>Contact / Submit</t>
+        </is>
+      </c>
+      <c r="G1" s="29" t="inlineStr">
+        <is>
+          <t>Why Danni Fits</t>
+        </is>
+      </c>
+      <c r="H1" s="29" t="inlineStr">
+        <is>
+          <t>In Person?</t>
+        </is>
+      </c>
+      <c r="I1" s="29" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="J1" s="29" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K1" s="29" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Collect Your Bag</t>
+        </is>
+      </c>
+      <c r="B2" s="30" t="inlineStr">
+        <is>
+          <t>Ebony Swank</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>Black women / Money &amp; Business</t>
+        </is>
+      </c>
+      <c r="D2" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E2" s="30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F2" s="30" t="inlineStr">
+        <is>
+          <t>collectyourbag.com or IG DM</t>
+        </is>
+      </c>
+      <c r="G2" s="30" t="inlineStr">
+        <is>
+          <t>Hustle-from-scratch story, money mindset, 'nobody is coming to save you' angle</t>
+        </is>
+      </c>
+      <c r="H2" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I2" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J2" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K2" s="30" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Blessed &amp; Bossed Up</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Monique Melton</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Black women / Faith &amp; Business</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>moniquemeltom.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Faith angle + resilience + community building matches her shelter work</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>The Black Girl Bravado</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>Undra Celeste</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Black women / Self-development</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>blackgirlbravado.com</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>Intersects brand, speaking, self-confidence -- she has all three stories</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K4" s="30" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rants &amp; Randomness</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Luvvie Ajayi Jones</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Black women / Culture &amp; Business</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Large (100K+)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Chicago / Remote</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>luvvie.org/podcast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Luvvie books cultural figures and storytellers -- Danni's Harvard + shelters story is Luvvie-coded</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Author of 'Professional Troublemaker'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>To Be Real</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>Ziwe Fumudoh</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Culture / Black women</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="G6" s="30" t="inlineStr">
+        <is>
+          <t>Cultural commentary + representation -- Ziwe covers body image and Blackness in media</t>
+        </is>
+      </c>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K6" s="30" t="inlineStr">
+        <is>
+          <t>More editorial, harder to pitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>The Read</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kid Fury &amp; Crissle West</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Black culture / Pop culture</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Very Large</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spotify / theread.libsyn.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Massive Black audience -- if they ever do guest interviews, she'd fit</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>More commentary format, limited guest slots</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Mogul Millennial</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Michelle Mekky (EP show)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Black / Business</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>mogulmillennial.com</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>Bootstrapped entrepreneur angle, Harvard credibility</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K8" s="30" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>The Strategy Hour</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Abagail Pumphrey &amp; Emylee Williams</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Women / Business &amp; Strategy</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>bossproject.com/podcast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Brand building + creator economy + organic growth story</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Earn Your Happy</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>Lori Harder</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Women / Mindset &amp; Business</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>Remote / LA</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>loriharder.com/podcast</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>Resilience + building without permission is a direct match</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Black Women Own the Conversation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Black women / Life</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Apple Podcasts search</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spaces made for her exact story</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>OWN Network podcast</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Maintenance Phase</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>Aubrey Gordon &amp; Michael Hobbes</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>Body politics / Media criticism</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>Very Large (500K+)</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>maintenancephase.com</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>Institute for Body Image + media literacy angle is a PERFECT pitch for this show</t>
+        </is>
+      </c>
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K12" s="30" t="inlineStr">
+        <is>
+          <t>THE body politics podcast -- academic + cultural. Danni's medical training work is exact fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>She's All Fat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>April K. &amp; Sophie Carter-Kahn</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fat positivity / Body liberation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>shesallfat.com</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fat positive space, lived experience of plus-size creator + advocate</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Direct body image podcast -- submit at shesallfat.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>Food Psych</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Christy Harrison, MPH, RD</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Anti-diet / HAES</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>Remote / NYC</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>christyharrison.com/foodpsych</t>
+        </is>
+      </c>
+      <c r="G14" s="30" t="inlineStr">
+        <is>
+          <t>Institute for Body Image trains medical professionals -- Christy's audience is exactly that world</t>
+        </is>
+      </c>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J14" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K14" s="30" t="inlineStr">
+        <is>
+          <t>Anti-diet dietitian; IBI co-creator angle is the hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fearless Rebelle Radio</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Summer Innanen</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Body image / Self-worth</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Remote / Canada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>summerinnanen.com/podcast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Body image coaching audience -- advocate + educator angle works</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>The Body Love Society</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>Dr. Jillian Murphy</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Body image / Wellness</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>bodylovesociety.com</t>
+        </is>
+      </c>
+      <c r="G16" s="30" t="inlineStr">
+        <is>
+          <t>IBI + medical professional angle -- she's building what this podcast promotes</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J16" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K16" s="30" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unsolicited: Fatties Talk Back</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Various hosts</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Fat activism / Body liberation</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Apple Podcasts</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lived experience + advocate work -- authentic fat activist space</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Fat liberation podcast</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>Your Body Is Not An Apology</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Sonya Renee Taylor</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>Body liberation / Social justice</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>thebodyisnotanapology.com/podcast</t>
+        </is>
+      </c>
+      <c r="G18" s="30" t="inlineStr">
+        <is>
+          <t>Body liberation AND racial justice -- her work spans both</t>
+        </is>
+      </c>
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J18" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K18" s="30" t="inlineStr">
+        <is>
+          <t>Sonya Renee Taylor's show</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>The Confidence Chronicles</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Self-confidence / Body</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Small-Mid</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Apple Podcasts search</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Confidence building at Harvard level AND shelter level -- rare range</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>The Influencer Podcast</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Julie Solomon</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Influencer / Brand growth</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>Remote / Nashville</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>juliesolomon.net/podcast</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="inlineStr">
+        <is>
+          <t>4% engagement rate story is a STANDOUT stat for this audience -- she teaches what Danni lives</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I20" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J20" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K20" s="30" t="inlineStr">
+        <is>
+          <t>Influencer marketing podcast</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Creator Economy Podcast</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Brady Shearer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Creator / Business</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>creatoreconomypodcast.com</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Building community vs just followers -- 52K with 4% engagement tells that story</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Black Girl Digital</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>Black women / Social media</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <t>blackgirldigital.com</t>
+        </is>
+      </c>
+      <c r="G22" s="30" t="inlineStr">
+        <is>
+          <t>Black creator + influencer niche -- direct fit</t>
+        </is>
+      </c>
+      <c r="H22" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J22" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K22" s="30" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Online Marketing Made Easy</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Amy Porterfield</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marketing / Business</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Very Large</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Remote / Nashville</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>amyporterfield.com/podcast</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Building without permission + brand deal story performs with this audience</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Harder to get booked, high payoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>Business of Social</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Sara Nguyen</t>
+        </is>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>Social media strategy</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F24" s="30" t="inlineStr">
+        <is>
+          <t>saranguyenco.com/podcast</t>
+        </is>
+      </c>
+      <c r="G24" s="30" t="inlineStr">
+        <is>
+          <t>Her engagement rate and community-building strategy is the hook</t>
+        </is>
+      </c>
+      <c r="H24" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J24" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K24" s="30" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ctrl Alt Delete</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Emma Gannon</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Creativity / Career / Digital</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UK / Remote</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emmagannon.co.uk/podcast</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Creative career built from scratch -- her story is very Ctrl Alt Delete coded</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>UK-based but global audience</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Side Hustle School</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Chris Guillebeau</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>Entrepreneurship / Hustle</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t>Very Large</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F26" s="30" t="inlineStr">
+        <is>
+          <t>sidehustleschool.com</t>
+        </is>
+      </c>
+      <c r="G26" s="30" t="inlineStr">
+        <is>
+          <t>Her speaking + brand + influencer three-track career is a perfect 'story' episode</t>
+        </is>
+      </c>
+      <c r="H26" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J26" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K26" s="30" t="inlineStr">
+        <is>
+          <t>Short story format -- pitch as a mini feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>We Can Do Hard Things</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Glennon Doyle</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Resilience / Women's empowerment</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Massive (millions)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Remote / FL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>wecandohardthings.com</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Glennon covers body image, representation, resilience -- Danni's life is a We Can Do Hard Things story</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Glennon is Florida-based (Naples) -- local angle possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>UnF*ck Your Brain</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Kara Loewentheil, JD</t>
+        </is>
+      </c>
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>Feminist mindset / Self-worth</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>Remote / NYC</t>
+        </is>
+      </c>
+      <c r="F28" s="30" t="inlineStr">
+        <is>
+          <t>unfuckyourbrain.com</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>Feminist lens on body image, media, self-worth -- IBI work is relevant</t>
+        </is>
+      </c>
+      <c r="H28" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J28" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K28" s="30" t="inlineStr">
+        <is>
+          <t>Harvard Law -- Harvard connection could be a hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Call Your Girlfriend</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ann Friedman &amp; Aminatou Sow</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Women / Culture / Politics</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>callyourgirlfriend.com</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cultural commentary, Black women, body politics -- her story fits this editorial space</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Dare to Lead</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Brené Brown</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>Leadership / Vulnerability</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>Massive</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
+        <is>
+          <t>Remote / TX</t>
+        </is>
+      </c>
+      <c r="F30" s="30" t="inlineStr">
+        <is>
+          <t>brenebrown.com/podcast</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>Vulnerability + resilience work -- shelters, Harvard, body image advocacy all speak to her framework</t>
+        </is>
+      </c>
+      <c r="H30" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" s="30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J30" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K30" s="30" t="inlineStr">
+        <is>
+          <t>Harder to get booked; very selective</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>The Marie Forleo Podcast</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Marie Forleo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Business / Mindset</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Very Large</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Remote / NYC</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>marieforleo.com/podcast</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Building from nothing, brand deals, speaking career -- multi-track creator story</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>The Boss Files</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Soledad O'Brien</t>
+        </is>
+      </c>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>Black women / Leadership</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>Mid-Large</t>
+        </is>
+      </c>
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>Remote / NYC</t>
+        </is>
+      </c>
+      <c r="F32" s="30" t="inlineStr">
+        <is>
+          <t>thebossfiles.com</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
+        <is>
+          <t>Soledad features real achievers -- Harvard + NPR + shelters is her type of guest</t>
+        </is>
+      </c>
+      <c r="H32" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J32" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K32" s="30" t="inlineStr">
+        <is>
+          <t>Soledad O'Brien is a journalist, so NPR/Vogue credentials matter</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>I Am That Girl</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alexis Jones</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Women's empowerment / Youth</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>iamthatgirl.com</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Girls' mentoring work + resilience talk directly aligns with their mission</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Youth empowerment focus -- shelter/mentoring work is the hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Self Made with Nely Galán</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Nely Galán</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>Latina / Women entrepreneurs</t>
+        </is>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E34" s="30" t="inlineStr">
+        <is>
+          <t>Miami / Remote</t>
+        </is>
+      </c>
+      <c r="F34" s="30" t="inlineStr">
+        <is>
+          <t>nelygalan.com</t>
+        </is>
+      </c>
+      <c r="G34" s="30" t="inlineStr">
+        <is>
+          <t>First-generation, self-made, no cosign -- aligns with 'nobody is coming to save you'</t>
+        </is>
+      </c>
+      <c r="H34" s="30" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I34" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J34" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K34" s="30" t="inlineStr">
+        <is>
+          <t>Miami-based; drive or fly for in-person</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>The Breakfast Club</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Charlamagne, Angela Yee, DJ Envy</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Black culture / Pop culture</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Massive</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>breakfastclubpower.com</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>National platform -- if she has a news hook (movie, book, major event), worth the pitch</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NYC studio; need strong news hook to get booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Big Tigger Radio Show / Podcast</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>Big Tigger</t>
+        </is>
+      </c>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>Atlanta / Black culture</t>
+        </is>
+      </c>
+      <c r="D36" s="30" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E36" s="30" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F36" s="30" t="inlineStr">
+        <is>
+          <t>V-103 / podcasts</t>
+        </is>
+      </c>
+      <c r="G36" s="30" t="inlineStr">
+        <is>
+          <t>Atlanta-based, Black audience, cultural touchpoint -- she visits Atlanta</t>
+        </is>
+      </c>
+      <c r="H36" s="30" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I36" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J36" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K36" s="30" t="inlineStr">
+        <is>
+          <t>Atlanta -- in-person possible (drive from Orlando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>The Quincy Podcast</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Orlando / Community</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Search Apple Podcasts 'Orlando'</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Local Orlando community show -- easy booking, local credibility</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Local visibility, easy win for community building</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>WFTV / WESH / WKMG Podcast Extensions</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>Various hosts</t>
+        </is>
+      </c>
+      <c r="C38" s="30" t="inlineStr">
+        <is>
+          <t>Orlando / Local news</t>
+        </is>
+      </c>
+      <c r="D38" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E38" s="30" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F38" s="30" t="inlineStr">
+        <is>
+          <t>Station websites</t>
+        </is>
+      </c>
+      <c r="G38" s="30" t="inlineStr">
+        <is>
+          <t>Local news podcasts or extensions -- her media-train resume makes her a credible local guest</t>
+        </is>
+      </c>
+      <c r="H38" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I38" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J38" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K38" s="30" t="inlineStr">
+        <is>
+          <t>Local Orlando TV stations with podcast extensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Atlanta Black Star Podcast</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Atlanta / Black culture &amp; politics</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>atlantablackstar.com</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cultural + social commentary -- representation + body image + media angles</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Atlanta -- in-person possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>The HBCU Experience</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>HBCUs / Black college life</t>
+        </is>
+      </c>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E40" s="30" t="inlineStr">
+        <is>
+          <t>Remote / Southeast</t>
+        </is>
+      </c>
+      <c r="F40" s="30" t="inlineStr">
+        <is>
+          <t>Apple Podcasts search</t>
+        </is>
+      </c>
+      <c r="G40" s="30" t="inlineStr">
+        <is>
+          <t>She spoke at Bethune-Cookman -- HBCU campus speaking angle is the hook</t>
+        </is>
+      </c>
+      <c r="H40" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J40" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K40" s="30" t="inlineStr">
+        <is>
+          <t>HBCU audience = direct pipeline to campus speaking gigs</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>The Speaker Lab</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Grant Baldwin</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Speaking industry</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Remote / Nashville</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>thespeakerlab.com/podcast</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>She is actively building her speaking career -- this audience books speakers AND refers them</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Industry podcast for speakers -- credibility building + direct client pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>Heroic Public Speaking</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>Michael &amp; Amy Port</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>Speaking / Performance</t>
+        </is>
+      </c>
+      <c r="D42" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E42" s="30" t="inlineStr">
+        <is>
+          <t>Remote / NYC</t>
+        </is>
+      </c>
+      <c r="F42" s="30" t="inlineStr">
+        <is>
+          <t>heroicpublicspeaking.com</t>
+        </is>
+      </c>
+      <c r="G42" s="30" t="inlineStr">
+        <is>
+          <t>Her NPR/TV background + stage presence story is content for this show</t>
+        </is>
+      </c>
+      <c r="H42" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J42" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K42" s="30" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Speaking of Speaking Podcast</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Speaking industry</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Small-Mid</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Apple Podcasts search</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Speaker community -- Harvard + shelters contrast is a booking story</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Niche but direct pipeline to booking opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>The Doctor's Farmacy</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="inlineStr">
+        <is>
+          <t>Dr. Mark Hyman</t>
+        </is>
+      </c>
+      <c r="C44" s="30" t="inlineStr">
+        <is>
+          <t>Functional medicine / Health</t>
+        </is>
+      </c>
+      <c r="D44" s="30" t="inlineStr">
+        <is>
+          <t>Very Large</t>
+        </is>
+      </c>
+      <c r="E44" s="30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F44" s="30" t="inlineStr">
+        <is>
+          <t>drhyman.com/podcast</t>
+        </is>
+      </c>
+      <c r="G44" s="30" t="inlineStr">
+        <is>
+          <t>IBI trains medical professionals -- inclusive care angle could bridge to his audience</t>
+        </is>
+      </c>
+      <c r="H44" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I44" s="30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J44" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K44" s="30" t="inlineStr">
+        <is>
+          <t>Hard to get booked; need strong health angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Body Justice</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Health equity / Fat liberation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Small-Mid</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Apple Podcasts search</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>IBI work training doctors in inclusive care -- health justice angle</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Health equity podcast -- IBI co-creator is the perfect hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>The Fat Doctor Podcast</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="inlineStr">
+        <is>
+          <t>Dr. Asher Larmie</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>HAES / Medical</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>Mid-tier</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>UK / Remote</t>
+        </is>
+      </c>
+      <c r="F46" s="30" t="inlineStr">
+        <is>
+          <t>thefatdoctor.co.uk</t>
+        </is>
+      </c>
+      <c r="G46" s="30" t="inlineStr">
+        <is>
+          <t>IBI trains medical professionals in body-positive care -- this is EXACTLY their audience</t>
+        </is>
+      </c>
+      <c r="H46" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I46" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J46" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K46" s="30" t="inlineStr">
+        <is>
+          <t>UK-based but global reach; IBI work is the hook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Email Tracker" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Brand Targets" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Podcast Targets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Conference Leads" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -700,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2604,6 +2605,1629 @@
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>University of North Florida -- Public Admin Dept</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>pubadmin@unf.edu</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Department Chair, MPA Program</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>@unflorida</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Danni's MPA alma mater -- WARM LEAD. Pitch: alumna returning to speak on public impact, storytelling, community resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>University of North Florida -- Student Life</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>studentaffairs@unf.edu</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Director of Student Life</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>@unflorida</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Alma mater. Campus-wide programming -- leadership and resilience talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>University of North Florida -- Women's Center</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Director, Women's Center</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>@unflorida</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Alma mater -- women's leadership/body image/media literacy programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Portland State University -- Sociology Dept</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Portland, OR</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Department Chair, Sociology</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>@portland_state</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Danni's BA Sociology alma mater -- WARM LEAD. Media literacy, representation, social structures talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Portland State University -- Student Activities</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Portland, OR</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Campus Programming Director</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>@portland_state</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Alma mater. Remote talk possible -- no travel needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>University of Central Florida -- Public Admin</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Chair, School of Public Administration</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>@ucfknights</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Local Orlando -- drive. Public administration angle + community storytelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>University of Central Florida -- Communications</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Chair, Nicholson School of Communication</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>@ucfknights</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Local -- social media, storytelling, media literacy is perfect for comm students</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>University of Central Florida -- Sociology</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Chair, Department of Sociology</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>@ucfknights</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Local Orlando -- representation, identity, community resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>University of Central Florida -- Student Union Programming</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Director, Student Activities</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>@ucfknights</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Largest university in the US -- campus event speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Rollins College -- Communications</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Winter Park, FL</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Chair, Communication Dept</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>@rollinscollege</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Small private liberal arts in Winter Park -- media literacy, personal brand talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Valencia College -- Student Life</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Director of Student Activities</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>@valenciacollege</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Largest community college in FL -- local, accessible, strong community programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Valencia College -- Social Science Dept</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Department Chair, Social Sciences</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>@valenciacollege</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Sociology/social science angle -- community resilience, media literacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Florida A&amp;M University -- Communications</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Dean, School of Journalism &amp; Graphic Communication</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>@famu_1887</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>HBCU -- social media + storytelling + representation is exactly right for this audience</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Florida A&amp;M University -- Student Programs</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Director, Student Activities</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>@famu_1887</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>HBCU campus programming -- 3hr drive from Orlando</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Florida International University -- Communications</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Chair, School of Communication + Journalism</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>@fiusocal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>FIU is majority-minority -- representation/media literacy talk fits</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Florida State University -- Sociology</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Chair, Department of Sociology</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>@floridastate</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Research-oriented -- bring Institute for Body Image angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>University of South Florida -- Marketing Dept</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Chair, Marketing Department</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>@usfbulls</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Marketing dept -- social media strategy, creator economy, personal brand building</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>University of Florida -- Public Relations</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Gainesville, FL</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Director, Public Relations Program</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>@universityofflorida</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Top PR program -- social media + authentic audience building is high-value content</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Florida Gulf Coast University -- Communications</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Chair, Communication &amp; Media</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>@fgcu</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Southwest FL -- 3hr drive</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Edward Waters University -- Student Programs</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Director of Student Life</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>@ewuniversity</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>HBCU in Jacksonville -- 2hr drive. Leadership and resilience talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Florida Memorial University -- Communications</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Miami Gardens, FL</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Chair, Communications</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>@floridamemorial</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>HBCU -- representation, storytelling, media literacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Spelman College -- Student Programs</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Director of Campus Programs</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>@spelmancollege</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Premier HBCU for Black women -- Harvard + shelters story resonates deeply</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Morehouse College -- Leadership Center</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Director, Leadership Programs</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>@morehousecollege</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Atlanta -- 5.5hr drive. Community building, resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Clark Atlanta University -- Marketing Dept</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Chair, Marketing Department</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>@clarkatlanta</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>HBCU -- social media + creator economy + brand building</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tuskegee University -- Student Programs</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tuskegee, AL</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Director of Student Activities</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>@tuskegeeu</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>HBCU -- 7hr drive from Orlando. Resilience/leadership talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>North Carolina A&amp;T -- Communications</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Greensboro, NC</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Chair, Journalism &amp; Mass Communication</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>@ncatsuaggies</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>HBCU with top journalism program -- social media + storytelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Georgia State University -- Marketing Dept</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Chair, Marketing Department</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>@georgiastateuniversity</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Atlanta -- social media, influencer economy, personal branding</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Georgia State University -- Communications</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Chair, Communication Department</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>@georgiastateuniversity</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Atlanta -- storytelling, media literacy, audience building</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>University of Georgia -- Grady School of Journalism</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Athens, GA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Dean, Grady College of Journalism</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>@universityofgeorgia</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Top journalism school -- social media influence + credibility story</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Boys &amp; Girls Clubs of Central Florida</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>407-896-0307</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Program Director / Youth Development</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>@bgcentralflorida</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Youth programming -- 'nobody is coming to save you' talk + self-confidence, dreaming big</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Boys &amp; Girls Clubs of Greater Orlando</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Program Director</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Youth mentoring -- resilience/leadership talk for teens</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>YMCA of Central Florida</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Youth Programs Director</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>@ymcacentralfl</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Youth and young adult programs -- leadership, confidence, goal-setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Girls Inc. of Greater Orlando</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Program Director</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Girls 6-18 -- confidence, media literacy, 'you are enough' messaging is exact fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Junior Achievement of Central Florida</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>jacao@jacentral.org</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Program Director</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>@jaorlando</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Already in Speaker Leads but pitch specifically to youth programs + entrepreneurship</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Orlando Youth Alliance</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Program Director</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>LGBTQ+ youth center in Orlando -- representation, identity, belonging</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Covenant House Florida</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>407-649-2256</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Program Director</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>@covenantfl</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Youth shelter/transitional housing -- she already does shelter talks. Direct fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SunServe Community Center</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Youth Program Coordinator</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>@sunservefl</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>LGBTQ+ community services including youth -- representation, identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Miami Dade County Youth Programs</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Director of Youth Services</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>County-level youth programming -- leadership, resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Urban League of Greater Orlando -- Youth</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Youth Program Manager</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>@nulp_cfl</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Urban League youth workforce development -- career + leadership talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>100 Black Men of Orlando</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Program Director</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Mentoring Black youth -- community resilience, leadership</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Jack and Jill of America -- Orlando Chapter</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Chapter President</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Established Black family organization -- youth leadership events</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Seminole State College -- Student Life</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sanford, FL</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Director of Student Life</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>@seminolestatefl</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Danni is a Sanford native -- LOCAL warm lead. Community college audience</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Daytona State College -- Student Programs</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Daytona Beach, FL</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Student Activities Director</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>@daytonastate</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>1hr from Orlando -- accessible drive</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Eastern Florida State College -- Communications</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Melbourne, FL</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Chair, Communications</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>@easternfloridastate</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1.5hr from Orlando</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -36406,7 +38030,6 @@
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
@@ -36736,7 +38359,6 @@
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
@@ -37070,7 +38692,6 @@
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
@@ -37290,7 +38911,6 @@
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
@@ -37400,7 +39020,6 @@
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
@@ -37844,7 +39463,6 @@
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
@@ -37954,7 +39572,6 @@
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
@@ -38804,6 +40421,1040 @@
       <c r="K46" s="30" t="inlineStr">
         <is>
           <t>UK-based but global reach; IBI work is the hook</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Conference Name</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="C1" s="29" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="inlineStr">
+        <is>
+          <t>Theme / Focus</t>
+        </is>
+      </c>
+      <c r="E1" s="29" t="inlineStr">
+        <is>
+          <t>Contact Title</t>
+        </is>
+      </c>
+      <c r="F1" s="29" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="29" t="inlineStr">
+        <is>
+          <t>Pitch Angle</t>
+        </is>
+      </c>
+      <c r="H1" s="29" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="I1" s="29" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="29" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>IAAPA Expo 2026</t>
+        </is>
+      </c>
+      <c r="B2" s="30" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>Nov 16-20, 2026</t>
+        </is>
+      </c>
+      <c r="D2" s="30" t="inlineStr">
+        <is>
+          <t>Global attractions &amp; entertainment industry</t>
+        </is>
+      </c>
+      <c r="E2" s="30" t="inlineStr">
+        <is>
+          <t>Program Director / Content Manager</t>
+        </is>
+      </c>
+      <c r="F2" s="30" t="inlineStr"/>
+      <c r="G2" s="30" t="inlineStr">
+        <is>
+          <t>Fireside or moderator on creator economy in entertainment, social media + venue marketing</t>
+        </is>
+      </c>
+      <c r="H2" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I2" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J2" s="30" t="inlineStr">
+        <is>
+          <t>Orange County Convention Center -- 1,100+ exhibitors. She is LOCAL Orlando talent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SHRM Annual Conference 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jun 16-19, 2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HR, workplace culture, leadership</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Conference Programming Chair</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fireside on storytelling, community building in the workplace -- NO DEI language</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Already passed June 2026 -- note for SHRM 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>AAPM&amp;R Annual Assembly 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Nov 11-14, 2026</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>Physical medicine &amp; rehabilitation, inclusive care</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>Program Committee Chair</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr"/>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>IBI co-creator angle -- inclusive, body-positive care in clinical settings. Fireside with a physician.</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>Institute for Body Image is the hook -- training medical professionals</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gaylord Palms Holiday Events 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kissimmee, FL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nov-Jan 2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Holiday experience, family, sponsorship activation</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Director of Events / PR</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Host/emcee for branded activation or fireside at holiday media event</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>christmasatgaylordpalms.com -- influencer/media partnership potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Dr. Phillips Center Frontyard Holiday Festival</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Dec 4 - Jan 4, 2026</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>Arts, culture, community</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>Director of Programming</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="inlineStr"/>
+      <c r="G6" s="30" t="inlineStr">
+        <is>
+          <t>Host or conversation partner for arts + community storytelling event</t>
+        </is>
+      </c>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>Free community event -- visibility + community credibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ABA (Association of Black Anthropologists) Annual</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Black culture, identity, community</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Program Chair</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Storytelling, representation, media + identity -- academic audience she can hold her own with (MPA, BA Sociology)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Atlanta -- 5.5hr drive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>National Conference of Black Political Scientists</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>Black politics, public administration, community</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>Program Chair</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr"/>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>MPA + public admin angle -- community resilience and social media as civic tools</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>Atlanta -- her MPA gives her credibility in this room</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>National Black MBA Association Conference</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Various (often Atlanta/Dallas)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Annual (Sept)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Black business, leadership, entrepreneurship</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Programming Director</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fireside on building a brand and business without traditional pathways</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>She fits the entrepreneurship track -- Harvard + no agent + brand deals</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>NABJ Convention 2026</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Annual (July/Aug)</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>Black journalism, media, storytelling</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>Programming Committee</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr"/>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>Fireside or panel on social media, creator economy, brand building for journalists</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>National Association of Black Journalists -- NPR + Vogue + media credentials are the hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>National Association of Black Accountants -- SE Region</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Annual (varies)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Black professionals, leadership</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Program Director</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Keynote or fireside: building without a safety net, financial + professional resilience</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Professional development audience -- resilience + community building talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>EssenceFest</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>New Orleans, LA</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>Annual (July)</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>Black women, culture, empowerment, business</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>Talent + Programming</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr"/>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>Fireside, panel, or conversation partner at the most important Black women's annual event</t>
+        </is>
+      </c>
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I12" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>THE event. Competitive to get into -- needs strong pitch and timing. Fly or drive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Florida Women's Conference</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Annual (fall)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Women in business, leadership, entrepreneurship</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Programming Director</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Keynote or fireside on building a platform without permission</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Local Orlando -- anchor event for women professionals</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>Women in Media Conference</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>Women in media, journalism, broadcasting</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>Program Director</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="inlineStr"/>
+      <c r="G14" s="30" t="inlineStr">
+        <is>
+          <t>Her TV/radio/social media resume -- on-camera to community builder journey</t>
+        </is>
+      </c>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I14" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J14" s="30" t="inlineStr">
+        <is>
+          <t>NPR + Jennifer Hudson + Tamron + TLC are the credentials</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BlogHer / SHEMedia Conference</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Various (major cities)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Women content creators, media, business</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Programming Lead</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Creator economy, engagement rate, 'building trust not just followers'</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Social media + creator space -- 4% engagement is the hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>Create &amp; Cultivate Conference</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>Various (LA, NYC, Atlanta)</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>Women entrepreneurs and creators</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>Programming Director</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr"/>
+      <c r="G16" s="30" t="inlineStr">
+        <is>
+          <t>Fireside: building a brand from a city that's not NY or LA</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I16" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J16" s="30" t="inlineStr">
+        <is>
+          <t>Creator/entrepreneur event -- 'nobody is coming to save you' is made for this stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Social Media Week</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Various (NY, Austin)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Social media, creator economy, marketing</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Content / Programming</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Social media strategy + engagement + community building -- her 4% rate is the hook</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Industry conference -- credibility builder for brand side</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>FCCLA State Leadership Conference</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>Annual (spring/fall)</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>Youth leadership, family &amp; consumer sciences</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>State Advisor / Program Director</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="inlineStr"/>
+      <c r="G18" s="30" t="inlineStr">
+        <is>
+          <t>Keynote: Perseverance, Grace &amp; Growth -- she has spoken at Seminole Leadership Conference</t>
+        </is>
+      </c>
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I18" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J18" s="30" t="inlineStr">
+        <is>
+          <t>Already in her speaking resume (Seminole Leadership). Ask for state-level invite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jack and Jill National Conference -- Youth Track</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Black youth leadership</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Youth Program Director</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leadership, resilience, social media as a tool for change</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Natural audience -- Black youth leadership</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>100 Black Men National Conference</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>Black youth mentoring, community</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>Program Chair</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr"/>
+      <c r="G20" s="30" t="inlineStr">
+        <is>
+          <t>Community impact + resilience + representation -- she already works with their demographic</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I20" s="30" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J20" s="30" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Girls Inc. National Conference</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Girls leadership, education, empowerment</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Conference Programming</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Media literacy, confidence, 'you are enough' -- exact fit for their mission</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>She already does this work at shelters and mentoring programs</t>
         </is>
       </c>
     </row>

--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2730,22 +2730,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Portland State University -- Sociology Dept</t>
+          <t>Florida State University -- Sociology Dept</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Department Chair, Sociology</t>
+          <t>Chair, Department of Sociology</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>@portland_state</t>
+          <t>@floridastate</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Portland State University -- Student Activities</t>
+          <t>Florida State University -- Student Activities</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Tallahassee, FL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>@portland_state</t>
+          <t>@floridastate</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Alma mater. Remote talk possible -- no travel needed</t>
+          <t>Alma mater. 3hr drive from Orlando. Strong HBCU-adjacent Black student population.</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Research-oriented -- bring Institute for Body Image angle</t>
+          <t>Already in tracker as general entry -- merge with alma mater warm lead. She has BA Sociology from FSU.</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Youth programming -- 'nobody is coming to save you' talk + self-confidence, dreaming big</t>
+          <t>ALUMNI -- she spent her entire childhood here. Open with: 'I grew up in your clubs.' Easiest booking on this list.</t>
         </is>
       </c>
     </row>
@@ -4226,6 +4226,411 @@
       <c r="K88" t="inlineStr">
         <is>
           <t>1.5hr from Orlando</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Lee County Black History Society</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>(239) 332-8778</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BlackHistory@LeeCountyBHS.org</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Executive Director / Board President</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>@leecountyblackhistorysociety</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>HERITAGE LEAD. She is a descendant of Nelson Tillis -- the first Black settler in Fort Myers, documented by THIS organization. Use fort_myers=True. They should be inviting her.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Williams Academy Black History Museum</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>(239) 332-8778</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BlackHistory@LeeCountyBHS.org</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Museum Director</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>HERITAGE LEAD. 1936 Henderson Ave -- operated by LCBHS. Nelson Tillis built the first school for Black children in FM; this museum is the institutional home of that story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FGCU -- Black Experience in Lee County Exhibit</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>FGCU Library Director / Community Engagement</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>@fgcu</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>HERITAGE LEAD. library.fgcu.edu/exhibits/lcbhs -- their exhibit opens with Nelson Tillis. She is a living descendant. This is a natural collaboration and press story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Fort Myers Community Redevelopment Agency</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>HERITAGE + PARTNERSHIP. They co-produced the Dunbar Cultural Landmarks Tour with LCBHS. Planning the $22M African American Cultural Center. She should be part of that conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Lee County Visitor &amp; Convention Bureau</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>(239) 338-3500</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VCB@LeeGov.com</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Brian Ososky, Chief Marketing Officer</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>@visitfortmyers</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>TOURISM PARTNERSHIP. Heritage travel + Black history tourism is a growing market. Her 52K Instagram reach (Orlando, Atlanta, Miami, NYC) is exactly their target demo. Use fort_myers=True.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>WGCU -- NPR/PBS Southwest Florida</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>News Director / Assignments Editor</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>@wgcu</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>PRESS. WGCU already covered Nelson Tillis (Feb 2023, Feb 2025). A living descendant with 52K Instagram and Harvard/NPR credentials coming home is a story they will want. Pitch as press, not speaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Gulfshore Life Magazine</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>239-321-7700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Stephanie Granada, Editor in Chief</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>@gulfshorelife</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>PRESS. SW Florida luxury lifestyle magazine. Heritage homecoming + Vogue + national TV + Harvard = their kind of story. Use fort_myers=True in press pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Gulfshore Business Magazine</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>239-498-8500</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>hcentrella@gulfshorebusiness.com</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Heidi Rambo Centrella, Editor in Chief</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>hcentrella@gulfshorebusiness.com</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>@gulfshorebusiness</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>PRESS. SW FL business media. IBI + brand partnerships + Fort Myers heritage = business + culture story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>City of Fort Myers -- Mayor's Office</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>239-321-7000</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Mayor Kevin B. Anderson / Community Liaison</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>@cityoffortmyers</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>PARTNERSHIP. Mayor Anderson -- she is the descendant of the man who built Fort Myers' first Black school. City recognition, proclamation, or partnership is not a stretch.</t>
         </is>
       </c>
     </row>
@@ -40576,7 +40981,6 @@
           <t>Conference Programming Chair</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Fireside on storytelling, community building in the workplace -- NO DEI language</t>
@@ -40672,7 +41076,6 @@
           <t>Director of Events / PR</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Host/emcee for branded activation or fireside at holiday media event</t>
@@ -40768,7 +41171,6 @@
           <t>Program Chair</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Storytelling, representation, media + identity -- academic audience she can hold her own with (MPA, BA Sociology)</t>
@@ -40864,7 +41266,6 @@
           <t>Programming Director</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Fireside on building a brand and business without traditional pathways</t>
@@ -40960,7 +41361,6 @@
           <t>Program Director</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Keynote or fireside: building without a safety net, financial + professional resilience</t>
@@ -41056,7 +41456,6 @@
           <t>Programming Director</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Keynote or fireside on building a platform without permission</t>
@@ -41152,7 +41551,6 @@
           <t>Programming Lead</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Creator economy, engagement rate, 'building trust not just followers'</t>
@@ -41248,7 +41646,6 @@
           <t>Content / Programming</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Social media strategy + engagement + community building -- her 4% rate is the hook</t>
@@ -41344,7 +41741,6 @@
           <t>Youth Program Director</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Leadership, resilience, social media as a tool for change</t>
@@ -41436,7 +41832,6 @@
           <t>Conference Programming</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Media literacy, confidence, 'you are enough' -- exact fit for their mission</t>

--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -4255,8 +4255,6 @@
           <t>Executive Director / Board President</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>@leecountyblackhistorysociety</t>
@@ -4304,9 +4302,6 @@
           <t>Museum Director</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>High</t>
@@ -4334,15 +4329,11 @@
           <t>Fort Myers, FL</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>FGCU Library Director / Community Engagement</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>@fgcu</t>
@@ -4375,16 +4366,11 @@
           <t>Fort Myers, FL</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Executive Director</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>High</t>
@@ -4424,11 +4410,14 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Brian Ososky, Chief Marketing Officer</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+          <t>Bryelle Benzing, Digital Marketing Manager (influencer lead)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>bbenzing@leegov.com</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>@visitfortmyers</t>
@@ -4446,7 +4435,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>TOURISM PARTNERSHIP. Heritage travel + Black history tourism is a growing market. Her 52K Instagram reach (Orlando, Atlanta, Miami, NYC) is exactly their target demo. Use fort_myers=True.</t>
+          <t>HERITAGE + INFLUENCER PITCH. Bryelle Benzing (bbenzing@leegov.com) is the first contact -- she runs influencer programs. Jackie Parker (jparker2@leegov.com) for press/FAM tours. CMO Brian Ososky (bososky@leegov.com) for high-level partnership. Use fort_myers=True. Nelson Tillis is Mural 11 in their River Basin Mural Project -- they already tell this story publicly.</t>
         </is>
       </c>
     </row>
@@ -4461,15 +4450,11 @@
           <t>Fort Myers, FL</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>News Director / Assignments Editor</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>@wgcu</t>
@@ -4487,7 +4472,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>PRESS. WGCU already covered Nelson Tillis (Feb 2023, Feb 2025). A living descendant with 52K Instagram and Harvard/NPR credentials coming home is a story they will want. Pitch as press, not speaker.</t>
+          <t>PRESS -- already covered Nelson Tillis in Feb 2023 and Feb 2025. A living descendant with 52K Instagram + Harvard + NPR credentials is a story they will run. Pitch as press contact, not speaker. wgcu.org</t>
         </is>
       </c>
     </row>
@@ -4507,14 +4492,11 @@
           <t>239-321-7700</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Stephanie Granada, Editor in Chief</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>@gulfshorelife</t>
@@ -4567,7 +4549,6 @@
           <t>hcentrella@gulfshorebusiness.com</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>@gulfshorebusiness</t>
@@ -4605,14 +4586,11 @@
           <t>239-321-7000</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Mayor Kevin B. Anderson / Community Liaison</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>@cityoffortmyers</t>

--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,8 +94,29 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00276221"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="007D6608"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -219,6 +240,26 @@
         <bgColor rgb="00F0F4FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F4F4F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -246,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -336,6 +377,18 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -701,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -715,6 +768,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -773,6 +827,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="L1" s="31" t="inlineStr">
+        <is>
+          <t>Research Needed</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -826,6 +885,11 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -867,6 +931,11 @@
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -912,6 +981,11 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -953,6 +1027,11 @@
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -994,6 +1073,11 @@
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1031,6 +1115,11 @@
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1072,6 +1161,11 @@
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1117,6 +1211,11 @@
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1162,6 +1261,11 @@
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1203,6 +1307,11 @@
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1244,6 +1353,11 @@
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1285,6 +1399,11 @@
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1326,6 +1445,11 @@
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1363,6 +1487,11 @@
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1404,6 +1533,11 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1445,6 +1579,11 @@
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1482,6 +1621,11 @@
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1523,6 +1667,11 @@
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1564,6 +1713,11 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1610,6 +1764,11 @@
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1663,6 +1822,11 @@
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1704,6 +1868,11 @@
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1753,6 +1922,11 @@
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="33" t="inlineStr">
+        <is>
+          <t>Name needed</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1798,6 +1972,11 @@
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1847,6 +2026,11 @@
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="33" t="inlineStr">
+        <is>
+          <t>Name needed</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1888,6 +2072,11 @@
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1921,6 +2110,11 @@
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1970,6 +2164,11 @@
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="33" t="inlineStr">
+        <is>
+          <t>Name needed</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2011,6 +2210,11 @@
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -2048,6 +2252,11 @@
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2089,6 +2298,11 @@
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -2130,6 +2344,11 @@
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -2175,6 +2394,11 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -2224,6 +2448,11 @@
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -2265,6 +2494,11 @@
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2306,6 +2540,11 @@
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -2359,6 +2598,11 @@
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2400,6 +2644,11 @@
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -2441,6 +2690,11 @@
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -2482,6 +2736,11 @@
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2523,6 +2782,11 @@
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -2564,6 +2828,11 @@
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -2605,6 +2874,11 @@
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="33" t="inlineStr">
+        <is>
+          <t>Name + email needed</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2647,6 +2921,11 @@
           <t>Danni's MPA alma mater -- WARM LEAD. Pitch: alumna returning to speak on public impact, storytelling, community resilience</t>
         </is>
       </c>
+      <c r="L45" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2689,6 +2968,11 @@
           <t>Alma mater. Campus-wide programming -- leadership and resilience talk</t>
         </is>
       </c>
+      <c r="L46" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2726,6 +3010,11 @@
           <t>Alma mater -- women's leadership/body image/media literacy programming</t>
         </is>
       </c>
+      <c r="L47" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2763,6 +3052,11 @@
           <t>Danni's BA Sociology alma mater -- WARM LEAD. Media literacy, representation, social structures talk</t>
         </is>
       </c>
+      <c r="L48" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2800,6 +3094,11 @@
           <t>Alma mater. 3hr drive from Orlando. Strong HBCU-adjacent Black student population.</t>
         </is>
       </c>
+      <c r="L49" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2837,6 +3136,11 @@
           <t>Local Orlando -- drive. Public administration angle + community storytelling</t>
         </is>
       </c>
+      <c r="L50" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2874,6 +3178,11 @@
           <t>Local -- social media, storytelling, media literacy is perfect for comm students</t>
         </is>
       </c>
+      <c r="L51" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2911,6 +3220,11 @@
           <t>Local Orlando -- representation, identity, community resilience</t>
         </is>
       </c>
+      <c r="L52" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2948,6 +3262,11 @@
           <t>Largest university in the US -- campus event speaker</t>
         </is>
       </c>
+      <c r="L53" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2985,6 +3304,11 @@
           <t>Small private liberal arts in Winter Park -- media literacy, personal brand talk</t>
         </is>
       </c>
+      <c r="L54" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3022,6 +3346,11 @@
           <t>Largest community college in FL -- local, accessible, strong community programming</t>
         </is>
       </c>
+      <c r="L55" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3059,6 +3388,11 @@
           <t>Sociology/social science angle -- community resilience, media literacy</t>
         </is>
       </c>
+      <c r="L56" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3096,6 +3430,11 @@
           <t>HBCU -- social media + storytelling + representation is exactly right for this audience</t>
         </is>
       </c>
+      <c r="L57" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3133,6 +3472,11 @@
           <t>HBCU campus programming -- 3hr drive from Orlando</t>
         </is>
       </c>
+      <c r="L58" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3170,6 +3514,11 @@
           <t>FIU is majority-minority -- representation/media literacy talk fits</t>
         </is>
       </c>
+      <c r="L59" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3207,6 +3556,11 @@
           <t>Already in tracker as general entry -- merge with alma mater warm lead. She has BA Sociology from FSU.</t>
         </is>
       </c>
+      <c r="L60" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3244,6 +3598,11 @@
           <t>Marketing dept -- social media strategy, creator economy, personal brand building</t>
         </is>
       </c>
+      <c r="L61" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3281,6 +3640,11 @@
           <t>Top PR program -- social media + authentic audience building is high-value content</t>
         </is>
       </c>
+      <c r="L62" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3318,6 +3682,11 @@
           <t>Southwest FL -- 3hr drive</t>
         </is>
       </c>
+      <c r="L63" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3355,6 +3724,11 @@
           <t>HBCU in Jacksonville -- 2hr drive. Leadership and resilience talk</t>
         </is>
       </c>
+      <c r="L64" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3392,6 +3766,11 @@
           <t>HBCU -- representation, storytelling, media literacy</t>
         </is>
       </c>
+      <c r="L65" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3429,6 +3808,11 @@
           <t>Premier HBCU for Black women -- Harvard + shelters story resonates deeply</t>
         </is>
       </c>
+      <c r="L66" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3466,6 +3850,11 @@
           <t>Atlanta -- 5.5hr drive. Community building, resilience</t>
         </is>
       </c>
+      <c r="L67" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3503,6 +3892,11 @@
           <t>HBCU -- social media + creator economy + brand building</t>
         </is>
       </c>
+      <c r="L68" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3540,6 +3934,11 @@
           <t>HBCU -- 7hr drive from Orlando. Resilience/leadership talk</t>
         </is>
       </c>
+      <c r="L69" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3577,6 +3976,11 @@
           <t>HBCU with top journalism program -- social media + storytelling</t>
         </is>
       </c>
+      <c r="L70" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3614,6 +4018,11 @@
           <t>Atlanta -- social media, influencer economy, personal branding</t>
         </is>
       </c>
+      <c r="L71" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3651,6 +4060,11 @@
           <t>Atlanta -- storytelling, media literacy, audience building</t>
         </is>
       </c>
+      <c r="L72" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3688,6 +4102,11 @@
           <t>Top journalism school -- social media influence + credibility story</t>
         </is>
       </c>
+      <c r="L73" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3730,6 +4149,11 @@
           <t>ALUMNI -- she spent her entire childhood here. Open with: 'I grew up in your clubs.' Easiest booking on this list.</t>
         </is>
       </c>
+      <c r="L74" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3762,6 +4186,11 @@
           <t>Youth mentoring -- resilience/leadership talk for teens</t>
         </is>
       </c>
+      <c r="L75" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3799,6 +4228,11 @@
           <t>Youth and young adult programs -- leadership, confidence, goal-setting</t>
         </is>
       </c>
+      <c r="L76" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3831,6 +4265,11 @@
           <t>Girls 6-18 -- confidence, media literacy, 'you are enough' messaging is exact fit</t>
         </is>
       </c>
+      <c r="L77" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3873,6 +4312,11 @@
           <t>Already in Speaker Leads but pitch specifically to youth programs + entrepreneurship</t>
         </is>
       </c>
+      <c r="L78" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3905,6 +4349,11 @@
           <t>LGBTQ+ youth center in Orlando -- representation, identity, belonging</t>
         </is>
       </c>
+      <c r="L79" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3947,6 +4396,11 @@
           <t>Youth shelter/transitional housing -- she already does shelter talks. Direct fit.</t>
         </is>
       </c>
+      <c r="L80" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3984,6 +4438,11 @@
           <t>LGBTQ+ community services including youth -- representation, identity</t>
         </is>
       </c>
+      <c r="L81" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4016,6 +4475,11 @@
           <t>County-level youth programming -- leadership, resilience</t>
         </is>
       </c>
+      <c r="L82" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4053,6 +4517,11 @@
           <t>Urban League youth workforce development -- career + leadership talk</t>
         </is>
       </c>
+      <c r="L83" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4085,6 +4554,11 @@
           <t>Mentoring Black youth -- community resilience, leadership</t>
         </is>
       </c>
+      <c r="L84" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4117,6 +4591,11 @@
           <t>Established Black family organization -- youth leadership events</t>
         </is>
       </c>
+      <c r="L85" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4154,6 +4633,11 @@
           <t>Danni is a Sanford native -- LOCAL warm lead. Community college audience</t>
         </is>
       </c>
+      <c r="L86" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4191,6 +4675,11 @@
           <t>1hr from Orlando -- accessible drive</t>
         </is>
       </c>
+      <c r="L87" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4228,6 +4717,11 @@
           <t>1.5hr from Orlando</t>
         </is>
       </c>
+      <c r="L88" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4275,6 +4769,11 @@
           <t>HERITAGE LEAD. She is a descendant of Nelson Tillis -- the first Black settler in Fort Myers, documented by THIS organization. Use fort_myers=True. They should be inviting her.</t>
         </is>
       </c>
+      <c r="L89" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4317,6 +4816,11 @@
           <t>HERITAGE LEAD. 1936 Henderson Ave -- operated by LCBHS. Nelson Tillis built the first school for Black children in FM; this museum is the institutional home of that story.</t>
         </is>
       </c>
+      <c r="L90" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4354,6 +4858,11 @@
           <t>HERITAGE LEAD. library.fgcu.edu/exhibits/lcbhs -- their exhibit opens with Nelson Tillis. She is a living descendant. This is a natural collaboration and press story.</t>
         </is>
       </c>
+      <c r="L91" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4386,6 +4895,11 @@
           <t>HERITAGE + PARTNERSHIP. They co-produced the Dunbar Cultural Landmarks Tour with LCBHS. Planning the $22M African American Cultural Center. She should be part of that conversation.</t>
         </is>
       </c>
+      <c r="L92" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4438,6 +4952,11 @@
           <t>HERITAGE + INFLUENCER PITCH. Bryelle Benzing (bbenzing@leegov.com) is the first contact -- she runs influencer programs. Jackie Parker (jparker2@leegov.com) for press/FAM tours. CMO Brian Ososky (bososky@leegov.com) for high-level partnership. Use fort_myers=True. Nelson Tillis is Mural 11 in their River Basin Mural Project -- they already tell this story publicly.</t>
         </is>
       </c>
+      <c r="L93" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4475,6 +4994,11 @@
           <t>PRESS -- already covered Nelson Tillis in Feb 2023 and Feb 2025. A living descendant with 52K Instagram + Harvard + NPR credentials is a story they will run. Pitch as press contact, not speaker. wgcu.org</t>
         </is>
       </c>
+      <c r="L94" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4517,6 +5041,11 @@
           <t>PRESS. SW Florida luxury lifestyle magazine. Heritage homecoming + Vogue + national TV + Harvard = their kind of story. Use fort_myers=True in press pitch.</t>
         </is>
       </c>
+      <c r="L95" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4569,6 +5098,11 @@
           <t>PRESS. SW FL business media. IBI + brand partnerships + Fort Myers heritage = business + culture story.</t>
         </is>
       </c>
+      <c r="L96" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4609,6 +5143,11 @@
       <c r="K97" t="inlineStr">
         <is>
           <t>PARTNERSHIP. Mayor Anderson -- she is the descendant of the man who built Fort Myers' first Black school. City recognition, proclamation, or partnership is not a stretch.</t>
+        </is>
+      </c>
+      <c r="L97" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
         </is>
       </c>
     </row>
@@ -29787,7 +30326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I199"/>
+  <dimension ref="A1:J199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -29799,6 +30338,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -29847,6 +30387,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="J1" s="31" t="inlineStr">
+        <is>
+          <t>Research Needed</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -29890,6 +30435,11 @@
           <t>Back-to-school toiletries giveaway since 2020 = natural story hook</t>
         </is>
       </c>
+      <c r="J2" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -29933,6 +30483,11 @@
           <t>Existing brand affinity. Already in her category.</t>
         </is>
       </c>
+      <c r="J3" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -29976,6 +30531,11 @@
           <t>Direct competitor to ELOQUII -- pitch one or the other first</t>
         </is>
       </c>
+      <c r="J4" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -30015,6 +30575,11 @@
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -30058,6 +30623,11 @@
           <t>Very strong values and audience alignment</t>
         </is>
       </c>
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -30101,6 +30671,11 @@
           <t>Back-to-school giveaway angle for toiletry brands</t>
         </is>
       </c>
+      <c r="J7" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -30144,6 +30719,11 @@
           <t>She's been doing back-to-school with a law firm every year since 2020. Kohl's is a natural sponsor.</t>
         </is>
       </c>
+      <c r="J8" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -30187,6 +30767,11 @@
           <t>Same back-to-school angle. Strong inclusive brand story.</t>
         </is>
       </c>
+      <c r="J9" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -30230,6 +30815,11 @@
           <t>She prefers sneakers and comfort. Crocs has a strong cultural moment right now.</t>
         </is>
       </c>
+      <c r="J10" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -30269,6 +30859,11 @@
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -30312,6 +30907,11 @@
           <t>Lemonade event late July 2026. Local Florida angle is strong.</t>
         </is>
       </c>
+      <c r="J12" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -30355,6 +30955,11 @@
           <t>Late-July Florida event -- beverage sponsor</t>
         </is>
       </c>
+      <c r="J13" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -30398,6 +31003,11 @@
           <t>Existing relationship -- follow up and deepen</t>
         </is>
       </c>
+      <c r="J14" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -30441,6 +31051,11 @@
           <t>Need formal testimonial quote. Already has the relationship.</t>
         </is>
       </c>
+      <c r="J15" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -30484,6 +31099,11 @@
           <t>National commercial credit. Leverage into ongoing creator partnership.</t>
         </is>
       </c>
+      <c r="J16" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -30527,6 +31147,11 @@
           <t>Just filmed with them. Strike while it is hot.</t>
         </is>
       </c>
+      <c r="J17" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -30570,6 +31195,11 @@
           <t>Existing relationship -- follow up</t>
         </is>
       </c>
+      <c r="J18" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -30617,6 +31247,11 @@
           <t>Also: PR@glamnetic.com / Wholesale@glamnetic.com -- send to Influencers@ first</t>
         </is>
       </c>
+      <c r="J19" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -30664,6 +31299,11 @@
           <t>Also: orders@impressbeauty.com -- help@ is the better contact for brand inquiry</t>
         </is>
       </c>
+      <c r="J20" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -30707,6 +31347,11 @@
           <t>Featured on Ulta's Black-owned/founded page. Find contact at sundayiisunday.com/pages/contact</t>
         </is>
       </c>
+      <c r="J21" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -30750,6 +31395,11 @@
           <t>Featured on Ulta's Black-owned/founded page</t>
         </is>
       </c>
+      <c r="J22" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -30793,6 +31443,11 @@
           <t>Featured on Ulta's Black-owned/founded page. Founder is public-facing -- can pitch directly on IG</t>
         </is>
       </c>
+      <c r="J23" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -30836,6 +31491,11 @@
           <t>Featured on Ulta's Black-owned/founded page</t>
         </is>
       </c>
+      <c r="J24" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -30879,6 +31539,11 @@
           <t>MUSE Accelerator (MUSEAccelerator@ulta.com) is for Black-OWNED brands, not influencers. Pitch through their creator/affiliate program instead.</t>
         </is>
       </c>
+      <c r="J25" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -30922,6 +31587,11 @@
           <t>ASOS is known for working with smaller creators. ASOS Curve is the exact fit.</t>
         </is>
       </c>
+      <c r="J26" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -30965,6 +31635,11 @@
           <t>They have a rep program. Apply at glossier.com or pitch directly via IG DM.</t>
         </is>
       </c>
+      <c r="J27" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -31008,6 +31683,11 @@
           <t>The Ordinary has a public affiliate/ambassador program. Good fit for educational skincare content.</t>
         </is>
       </c>
+      <c r="J28" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -31051,6 +31731,11 @@
           <t>Lower priority. Only pursue if she wants to lean into natural hair content more.</t>
         </is>
       </c>
+      <c r="J29" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -31098,6 +31783,11 @@
           <t>Direct email in hand. Send today.</t>
         </is>
       </c>
+      <c r="J30" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -31145,6 +31835,11 @@
           <t>Personal contact email. Mention her audience and style content.</t>
         </is>
       </c>
+      <c r="J31" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -31188,6 +31883,11 @@
           <t>No direct email. Apply through Ambassador Application on their site.</t>
         </is>
       </c>
+      <c r="J32" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -31231,6 +31931,11 @@
           <t>No direct email. Apply through their Ambassador Application.</t>
         </is>
       </c>
+      <c r="J33" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -31274,6 +31979,11 @@
           <t>No direct email. Apply through their Ambassador Program.</t>
         </is>
       </c>
+      <c r="J34" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -31321,6 +32031,11 @@
           <t>Direct email. Small brand = more flexibility, faster reply. Pitch personal and specific.</t>
         </is>
       </c>
+      <c r="J35" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -31368,6 +32083,11 @@
           <t>Direct email. Strong brand with proven creator program. High priority.</t>
         </is>
       </c>
+      <c r="J36" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -31411,6 +32131,11 @@
           <t>No direct email. Contact via form on website. Worth the effort given the cultural fit.</t>
         </is>
       </c>
+      <c r="J37" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -31454,6 +32179,11 @@
           <t>No direct email. Contact via form. Black-owned -- strong pitch angle.</t>
         </is>
       </c>
+      <c r="J38" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -31501,6 +32231,11 @@
           <t>Direct email. One of the most recognized names in the lash space.</t>
         </is>
       </c>
+      <c r="J39" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -31548,6 +32283,11 @@
           <t>Direct email. Pitch her as a regular lash wearer who can create authentic content.</t>
         </is>
       </c>
+      <c r="J40" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -31595,6 +32335,11 @@
           <t>incubator@lashify.com is purpose-built for creator deals. This is the strongest contact in the lash category. Send soon.</t>
         </is>
       </c>
+      <c r="J41" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -31642,6 +32387,11 @@
           <t>Direct email. Natural hair creator content. Pitch around her hair journey.</t>
         </is>
       </c>
+      <c r="J42" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -31687,6 +32437,11 @@
       <c r="I43" s="4" t="inlineStr">
         <is>
           <t>The email address 'curlfriends' is literally their creator/community contact. Strong signal they want partnerships.</t>
+        </is>
+      </c>
+      <c r="J43" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
     </row>
@@ -31728,6 +32483,11 @@
           <t>Contact form only. Low priority unless she specifically likes this brand.</t>
         </is>
       </c>
+      <c r="J44" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -31771,6 +32531,11 @@
           <t>ADHD niche is growing fast with creators. Tiimo actively works with ADHD creators. Pitch as someone who understands the lived experience.</t>
         </is>
       </c>
+      <c r="J45" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -31814,6 +32579,11 @@
           <t>Smaller app = faster deal, more flexibility. Good entry into the ADHD creator space.</t>
         </is>
       </c>
+      <c r="J46" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -31857,6 +32627,11 @@
           <t>They have a creator affiliate program. Lower-effort pitch.</t>
         </is>
       </c>
+      <c r="J47" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -31900,6 +32675,11 @@
           <t>Newer, smaller product. Good for authentic ADHD content if she is open about it.</t>
         </is>
       </c>
+      <c r="J48" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -31943,6 +32723,11 @@
           <t>Large platform. Works with creators in the wellness and mindfulness space.</t>
         </is>
       </c>
+      <c r="J49" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -31986,6 +32771,11 @@
           <t>More selective than smaller apps. Worth pitching but may need more growth first. Revisit at 75K.</t>
         </is>
       </c>
+      <c r="J50" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -32029,6 +32819,11 @@
           <t>Calm does big influencer deals. At 52K they may engage -- pitch the 4% engagement and community trust angle over raw follower count.</t>
         </is>
       </c>
+      <c r="J51" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -32072,6 +32867,11 @@
           <t>FLAG: BetterHelp had controversy in 2022 over creator partnerships without proper therapy disclaimers. They have cleaned this up, but read their current creator terms carefully before signing anything. The pay is real -- just protect yourself.</t>
         </is>
       </c>
+      <c r="J52" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -32119,6 +32919,11 @@
           <t>Florida-based, family-owned. They sponsor local events. Strong local creator angle. Pitch: Orlando creator, local following, home lifestyle content.</t>
         </is>
       </c>
+      <c r="J53" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -32162,6 +32967,11 @@
           <t>Sister brand to Ashley HomeStore. Florida-headquartered. Contact via cityfurniture.com/about/contact</t>
         </is>
       </c>
+      <c r="J54" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -32205,6 +33015,11 @@
           <t>Rooms To Go HQ is in Seffner, FL. Local Florida angle is real.</t>
         </is>
       </c>
+      <c r="J55" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -32248,6 +33063,11 @@
           <t>Publix does not do traditional influencer deals, but they sponsor local community events -- back-to-school event angle is strong here.</t>
         </is>
       </c>
+      <c r="J56" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -32295,6 +33115,11 @@
           <t>Visit Orlando actively recruits local and regional content creators. Pitch as the face of an authentic Orlando story.</t>
         </is>
       </c>
+      <c r="J57" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -32338,6 +33163,11 @@
           <t>Visit Florida has a formal press/creator program. Find contact at visitflorida.org/media</t>
         </is>
       </c>
+      <c r="J58" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -32381,6 +33211,11 @@
           <t>Local Orlando hotel chain. Community-oriented brand. Her back-to-school event and community work is the right angle.</t>
         </is>
       </c>
+      <c r="J59" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -32424,6 +33259,11 @@
           <t>Universal partner. Music and culture angle.</t>
         </is>
       </c>
+      <c r="J60" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -32467,6 +33307,11 @@
           <t>Multiple Orlando properties. Creator-friendly hospitality brand.</t>
         </is>
       </c>
+      <c r="J61" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -32514,6 +33359,11 @@
           <t>Universal has an active local creator program. Her Orlando identity is the hook.</t>
         </is>
       </c>
+      <c r="J62" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -32557,6 +33407,11 @@
           <t>Apply at creator.marriott.com or pitch via partnerships@marriott.com. Already has Hilton credential to reference.</t>
         </is>
       </c>
+      <c r="J63" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -32600,6 +33455,11 @@
           <t>She travels for speaking engagements. Travel content is a natural byproduct of her speaker life.</t>
         </is>
       </c>
+      <c r="J64" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -32643,6 +33503,11 @@
           <t>Hilton and Omni are comparable tiers. Existing hotel brand credit opens this.</t>
         </is>
       </c>
+      <c r="J65" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -32690,6 +33555,11 @@
           <t>Carnival is headquartered in Miami. Her Florida base is the hook. They have an active creator program.</t>
         </is>
       </c>
+      <c r="J66" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -32733,6 +33603,11 @@
           <t>RCL HQ is in Miami. Strong creator program. Her Florida-based travel content angle works.</t>
         </is>
       </c>
+      <c r="J67" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -32776,6 +33651,11 @@
           <t>NCL HQ is Miami. Similar pitch to Royal Caribbean.</t>
         </is>
       </c>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
@@ -32819,6 +33699,11 @@
           <t>Southwest has a Community Relations team and a Rapid Rewards ambassador program. Her speaking travel is authentic.</t>
         </is>
       </c>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -32862,6 +33747,11 @@
           <t>JetBlue has done notable creator campaigns. Florida is a key market for them.</t>
         </is>
       </c>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
@@ -32909,6 +33799,11 @@
           <t>FabFitFun does massive influencer campaigns. Her audience demo is exactly theirs. Send this week.</t>
         </is>
       </c>
+      <c r="J71" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -32956,6 +33851,11 @@
           <t>Ipsy has a large creator network. Direct email known. Strong fit.</t>
         </is>
       </c>
+      <c r="J72" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -32999,6 +33899,11 @@
           <t>Pitch the Stitch Fix Plus angle. She gets styled boxes delivered -- authentic content opportunity.</t>
         </is>
       </c>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -33042,6 +33947,11 @@
           <t>RTR has a plus-size inventory. Her event/speaking lifestyle is an authentic use case.</t>
         </is>
       </c>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
@@ -33085,6 +33995,11 @@
           <t>ThredUp's Clean Out Kit + styling content is popular with millennial creators.</t>
         </is>
       </c>
+      <c r="J75" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -33128,6 +34043,11 @@
           <t>Poppi does heavy influencer campaigns. Lemonade/beverage angle for late-July event. Send this month.</t>
         </is>
       </c>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -33171,6 +34091,11 @@
           <t>OLIPOP is aggressively expanding creator deals. Her wellness/body positive platform aligns.</t>
         </is>
       </c>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -33214,6 +34139,11 @@
           <t>Liquid I.V. has a large creator program. Active lifestyle + travel = natural content.</t>
         </is>
       </c>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
@@ -33257,6 +34187,11 @@
           <t>Events, Florida summer, staying clear-headed -- authentic content possibilities.</t>
         </is>
       </c>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -33300,6 +34235,11 @@
           <t>Canva Education and Creator programs exist. She makes media kits, graphics -- authentic user.</t>
         </is>
       </c>
+      <c r="J80" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
@@ -33347,6 +34287,11 @@
           <t>Bumble pays well and their campaigns focus on women's empowerment -- exact alignment. Also: Bumble BFF is a real fit for her community-building message.</t>
         </is>
       </c>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -33390,6 +34335,11 @@
           <t>Hinge has done creator campaigns. Less obvious fit than Bumble but worth pitching.</t>
         </is>
       </c>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -33433,6 +34383,11 @@
           <t>More of a stretch -- only pursue if she creates outdoor/gathering content.</t>
         </is>
       </c>
+      <c r="J83" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -33476,6 +34431,11 @@
           <t>Turo has a creator program. Florida-based road trips, travel-for-speaking content.</t>
         </is>
       </c>
+      <c r="J84" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -33519,6 +34479,11 @@
           <t>Knix is explicitly body-positive and runs extensive creator campaigns. Strong values match.</t>
         </is>
       </c>
+      <c r="J85" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -33562,6 +34527,11 @@
           <t>Thinx does creator campaigns. Women's health + body acceptance angle.</t>
         </is>
       </c>
+      <c r="J86" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -33605,6 +34575,11 @@
           <t>Clean period care brand with a strong millennial following.</t>
         </is>
       </c>
+      <c r="J87" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -33648,6 +34623,11 @@
           <t>She is already in YITTY/Fabletics. Spanx partnership would require checking exclusivity. Note that.</t>
         </is>
       </c>
+      <c r="J88" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="42" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
@@ -33691,6 +34671,11 @@
           <t>DoorDash runs seasonal creator campaigns. Easy lifestyle integration.</t>
         </is>
       </c>
+      <c r="J89" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="42" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -33734,6 +34719,11 @@
           <t>Competing with DoorDash -- pitch one at a time.</t>
         </is>
       </c>
+      <c r="J90" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="42" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
@@ -33781,6 +34771,11 @@
           <t>HelloFresh has a large influencer program. Direct email known.</t>
         </is>
       </c>
+      <c r="J91" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="42" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -33824,6 +34819,11 @@
           <t>Premium plus-size brand. Strong values alignment. She wears 22/24.</t>
         </is>
       </c>
+      <c r="J92" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="42" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
@@ -33867,6 +34867,11 @@
           <t>Body positive, size-inclusive, Black-founded adjacent culture. Strong fit.</t>
         </is>
       </c>
+      <c r="J93" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="42" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -33910,6 +34915,11 @@
           <t>Girlfriend Collective actively recruits diverse creators. XS-6XL range.</t>
         </is>
       </c>
+      <c r="J94" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="42" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
@@ -33953,6 +34963,11 @@
           <t>High-end plus-size. Her Vogue editorial and media presence positions her for this tier.</t>
         </is>
       </c>
+      <c r="J95" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="42" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -33996,6 +35011,11 @@
           <t>Direct product fit. She gets clothes she'd actually wear -- authentic content opportunity.</t>
         </is>
       </c>
+      <c r="J96" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="42" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
@@ -34039,6 +35059,11 @@
           <t>Ritual has a large creator program. Women's health + self-care angle.</t>
         </is>
       </c>
+      <c r="J97" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="42" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -34082,6 +35107,11 @@
           <t>Hers has mental health and body care products. Creator program exists.</t>
         </is>
       </c>
+      <c r="J98" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="42" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
@@ -34125,6 +35155,11 @@
           <t>Large influencer program. Authentic skincare content opportunity.</t>
         </is>
       </c>
+      <c r="J99" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="42" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -34168,6 +35203,11 @@
           <t>Spotify for Podcasters and Spotify Creator programs exist. Her voice + storytelling background is the pitch.</t>
         </is>
       </c>
+      <c r="J100" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="42" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
@@ -34211,6 +35251,11 @@
           <t>Her NPR credit is a credential here. Pitch as a cultural voice, not just a creator.</t>
         </is>
       </c>
+      <c r="J101" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="42" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -34254,6 +35299,11 @@
           <t>Cash App is one of the biggest spenders in Black creator marketing. Her audience is exactly theirs.</t>
         </is>
       </c>
+      <c r="J102" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
@@ -34297,6 +35347,11 @@
           <t>Chime targets unbanked/underbanked communities and does heavy creator marketing.</t>
         </is>
       </c>
+      <c r="J103" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -34340,6 +35395,11 @@
           <t>Pitch as a community event organizer, not just an influencer. She has a track record.</t>
         </is>
       </c>
+      <c r="J104" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="42" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
@@ -34383,6 +35443,11 @@
           <t>Lower priority but Etsy has influencer partnerships around creator economy content.</t>
         </is>
       </c>
+      <c r="J105" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="42" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -34426,6 +35491,11 @@
           <t>Sun Bum is Cocoa Beach, FL founded. Perfect Florida story. Lemonade event sun care sponsor.</t>
         </is>
       </c>
+      <c r="J106" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="42" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
@@ -34469,6 +35539,11 @@
           <t>Summer Florida event sponsor angle. Back-to-school outdoor event.</t>
         </is>
       </c>
+      <c r="J107" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="42" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -34512,6 +35587,11 @@
           <t>Summer outdoor event, back-to-school outdoor angle.</t>
         </is>
       </c>
+      <c r="J108" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="42" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
@@ -34555,6 +35635,11 @@
           <t>She co-created Institute for Body Image with medical professionals -- premium sunscreen has a wellness angle.</t>
         </is>
       </c>
+      <c r="J109" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="42" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -34598,6 +35683,11 @@
           <t>Summer outdoor event, hydration, Florida lifestyle.</t>
         </is>
       </c>
+      <c r="J110" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="42" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
@@ -34641,6 +35731,11 @@
           <t>A Stanley x lemonade event collab is practically a meme at this point -- and that is why it works.</t>
         </is>
       </c>
+      <c r="J111" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="42" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -34684,6 +35779,11 @@
           <t>Event sponsor for lemonade/outdoor event. YETI coolers at a summer gathering = natural content.</t>
         </is>
       </c>
+      <c r="J112" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="42" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
@@ -34731,6 +35831,11 @@
           <t>Simple Modern actively recruits mid-size creators. Direct email found. Summer event angle.</t>
         </is>
       </c>
+      <c r="J113" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="42" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -34774,6 +35879,11 @@
           <t>Kia's brand refresh targets millennials of color. Her speaking travel is authentic car content.</t>
         </is>
       </c>
+      <c r="J114" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="42" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
@@ -34817,6 +35927,11 @@
           <t>Toyota has a dedicated multicultural marketing team. Her audience is exactly their target.</t>
         </is>
       </c>
+      <c r="J115" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="42" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -34860,6 +35975,11 @@
           <t>Hyundai has done creator campaigns with lifestyle and culture-focused women creators.</t>
         </is>
       </c>
+      <c r="J116" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="42" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
@@ -34903,6 +36023,11 @@
           <t>Lower priority but less competitive than other car brands for her audience.</t>
         </is>
       </c>
+      <c r="J117" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="42" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -34946,6 +36071,11 @@
           <t>Already in tracker -- verify not duplicate. Turo is worth pitching twice if needed.</t>
         </is>
       </c>
+      <c r="J118" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="42" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
@@ -34989,6 +36119,11 @@
           <t>Her Sixt national commercial is a direct credential for car brand pitches. Enterprise is everywhere in FL.</t>
         </is>
       </c>
+      <c r="J119" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="42" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -35032,6 +36167,11 @@
           <t>Her TLC, Jennifer Hudson Show, Tamron Hall credits all live on NBC/streaming universe. Natural pitch.</t>
         </is>
       </c>
+      <c r="J120" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
@@ -35075,6 +36215,11 @@
           <t>Hulu targets millennials and diverse audiences heavily.</t>
         </is>
       </c>
+      <c r="J121" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -35118,6 +36263,11 @@
           <t>Her actress credits make this a dual pitch -- content creator AND talent.</t>
         </is>
       </c>
+      <c r="J122" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
@@ -35161,6 +36311,11 @@
           <t>Tubi's audience is Black millennials. She is Black, millennial, on-camera talent. Fast yes.</t>
         </is>
       </c>
+      <c r="J123" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -35204,6 +36359,11 @@
           <t>She HAS ALREADY HOSTED a BET event. This is a warm pitch, not cold outreach. Lead with that.</t>
         </is>
       </c>
+      <c r="J124" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="42" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
@@ -35247,6 +36407,11 @@
           <t>OWN's audience is literally 'Danni Adams fans who haven't found her yet.'</t>
         </is>
       </c>
+      <c r="J125" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="42" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -35290,6 +36455,11 @@
           <t>Method works with lifestyle and home content creators. Millennial household angle.</t>
         </is>
       </c>
+      <c r="J126" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="42" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
@@ -35333,6 +36503,11 @@
           <t>Mrs. Meyer's has done creator campaigns. Natural, feel-good home products.</t>
         </is>
       </c>
+      <c r="J127" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="42" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -35376,6 +36551,11 @@
           <t>Grove works with millennial women creators on sustainable living content.</t>
         </is>
       </c>
+      <c r="J128" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="42" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
@@ -35419,6 +36599,11 @@
           <t>Lower priority but P&amp;G brands run constant creator campaigns.</t>
         </is>
       </c>
+      <c r="J129" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -35462,6 +36647,11 @@
           <t>OXO works with lifestyle and home creators. Entry-level brand deal.</t>
         </is>
       </c>
+      <c r="J130" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
@@ -35509,6 +36699,11 @@
           <t>MasterClass features people with lived expertise. Her Harvard speaker + Institute for Body Image credentials are exactly the MasterClass profile.</t>
         </is>
       </c>
+      <c r="J131" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="42" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -35552,6 +36747,11 @@
           <t>Her 'Nobody Is Coming to Save You' talk is a LinkedIn article waiting to happen. Creator partnerships here are real.</t>
         </is>
       </c>
+      <c r="J132" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="42" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
@@ -35595,6 +36795,11 @@
           <t>She runs workshops. Skillshare is literally a platform for her workshop content. Natural deal.</t>
         </is>
       </c>
+      <c r="J133" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="42" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -35638,6 +36843,11 @@
           <t>Her social media and storytelling workshops could live on Udemy as a course.</t>
         </is>
       </c>
+      <c r="J134" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
@@ -35681,6 +36891,11 @@
           <t>Long play. Credibility angle more than product angle.</t>
         </is>
       </c>
+      <c r="J135" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="42" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -35724,6 +36939,11 @@
           <t>Local Florida chain. Community partnership angle, back-to-school or lemonade event co-sponsor.</t>
         </is>
       </c>
+      <c r="J136" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="42" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
@@ -35767,6 +36987,11 @@
           <t>Wawa does community sponsorships in FL. Her community events angle is the pitch.</t>
         </is>
       </c>
+      <c r="J137" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="42" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -35810,6 +37035,11 @@
           <t>Summer event, health and wellness, Florida presence. Easy product integration.</t>
         </is>
       </c>
+      <c r="J138" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="42" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
@@ -35853,6 +37083,11 @@
           <t>Florida brand, summer event, health-forward. Her lemonade event could co-brand with a smoothie chain.</t>
         </is>
       </c>
+      <c r="J139" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="42" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
@@ -35896,6 +37131,11 @@
           <t>Back-to-school event. Chick-fil-A does local community event sponsorships in the South.</t>
         </is>
       </c>
+      <c r="J140" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
@@ -35939,6 +37179,11 @@
           <t>Financial empowerment + millennial women = Acorns' audience. Her independence message is on-brand.</t>
         </is>
       </c>
+      <c r="J141" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="42" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -35982,6 +37227,11 @@
           <t>SoFi targets millennial professionals. Her speaker/entrepreneur identity is their customer.</t>
         </is>
       </c>
+      <c r="J142" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="42" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
@@ -36025,6 +37275,11 @@
           <t>Her lemonade event + Lemonade Insurance is a pitch that writes itself. 'Life gives you lemons, your insurance should not.' Send this one.</t>
         </is>
       </c>
+      <c r="J143" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="42" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
@@ -36068,6 +37323,11 @@
           <t>She drives for speaking gigs. Car insurance for independent millennial women is the angle.</t>
         </is>
       </c>
+      <c r="J144" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="42" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
@@ -36111,6 +37371,11 @@
           <t>Fenty's core audience is Black women who prioritize inclusive shade ranges. She IS the customer.</t>
         </is>
       </c>
+      <c r="J145" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="42" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -36154,6 +37419,11 @@
           <t>Her Vogue editorial and luxury brand history (Hilton, Sixt) positions her for premium beauty pitches.</t>
         </is>
       </c>
+      <c r="J146" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="42" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
@@ -36197,6 +37467,11 @@
           <t>Natural extension of Fenty Beauty pitch -- pitch both together.</t>
         </is>
       </c>
+      <c r="J147" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="42" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -36240,6 +37515,11 @@
           <t>e.l.f. runs constant micro and mid-tier creator campaigns. Her 4% engagement is their dream metric.</t>
         </is>
       </c>
+      <c r="J148" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="42" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
@@ -36283,6 +37563,11 @@
           <t>NYX has a strong Black creator history. Bold, expressive looks align with her brand energy.</t>
         </is>
       </c>
+      <c r="J149" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="42" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -36326,6 +37611,11 @@
           <t>NARS does creator campaigns. Her editorial credits make this a realistic pitch.</t>
         </is>
       </c>
+      <c r="J150" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="42" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
@@ -36369,6 +37659,11 @@
           <t>Premium brand. Her media credits and Hilton/Sixt partnerships establish her at this tier.</t>
         </is>
       </c>
+      <c r="J151" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="42" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
@@ -36412,6 +37707,11 @@
           <t>Sol de Janeiro is having a massive cultural moment. Florida + summer + her audience = natural fit. Pitch now.</t>
         </is>
       </c>
+      <c r="J152" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="42" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
@@ -36455,6 +37755,11 @@
           <t>Miami-born sunscreen brand. Florida, summer, nostalgia, millennials -- she fits every box.</t>
         </is>
       </c>
+      <c r="J153" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="42" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
@@ -36498,6 +37803,11 @@
           <t>Native runs consistent creator campaigns. Natural, clean body care -- her wellness angle.</t>
         </is>
       </c>
+      <c r="J154" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="42" customHeight="1">
       <c r="A155" s="4" t="inlineStr">
@@ -36541,6 +37851,11 @@
           <t>Beekman 1802 actively recruits mid-tier creators. Their audience overlaps with hers significantly.</t>
         </is>
       </c>
+      <c r="J155" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="42" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -36584,6 +37899,11 @@
           <t>Old Navy Navyist program and creator deals. Inclusive sizing, accessible price, her audience shops here.</t>
         </is>
       </c>
+      <c r="J156" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="42" customHeight="1">
       <c r="A157" s="4" t="inlineStr">
@@ -36627,6 +37947,11 @@
           <t>Lower priority but H&amp;M does constant creator activations.</t>
         </is>
       </c>
+      <c r="J157" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="42" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -36670,6 +37995,11 @@
           <t>Nordstrom Trunk Club and their creator program. Her Vogue credit opens this door.</t>
         </is>
       </c>
+      <c r="J158" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="42" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
@@ -36713,6 +38043,11 @@
           <t>Black-owned plus-size brand. Her audience buys this. Her size 22/24 is their model size.</t>
         </is>
       </c>
+      <c r="J159" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="42" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
@@ -36756,6 +38091,11 @@
           <t>Ashley Stewart is THE plus-size brand for Black women. This should have been on the list from day one.</t>
         </is>
       </c>
+      <c r="J160" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="42" customHeight="1">
       <c r="A161" s="4" t="inlineStr">
@@ -36799,6 +38139,11 @@
           <t>Steve Madden does creator campaigns. Kitten heels and statement shoes align with her style.</t>
         </is>
       </c>
+      <c r="J161" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="42" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -36842,6 +38187,11 @@
           <t>Kitten heels + classic styles. Her fashion content angle.</t>
         </is>
       </c>
+      <c r="J162" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="42" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
@@ -36885,6 +38235,11 @@
           <t>New Balance has leaned into culture and diverse creators. Her sneaker preference and lifestyle fit.</t>
         </is>
       </c>
+      <c r="J163" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="42" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -36928,6 +38283,11 @@
           <t>HOKA is everywhere right now with millennial women. Comfort + style is her footwear brand.</t>
         </is>
       </c>
+      <c r="J164" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="42" customHeight="1">
       <c r="A165" s="4" t="inlineStr">
@@ -36971,6 +38331,11 @@
           <t>Skechers does creator campaigns and has wide-width options. Comfort creator content.</t>
         </is>
       </c>
+      <c r="J165" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -37008,6 +38373,11 @@
           <t>chocolatekingdom.com -- small enough to go direct to owner for gifted collab</t>
         </is>
       </c>
+      <c r="J166" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -37045,6 +38415,11 @@
           <t>waldorfastoriaorlando.com -- complex marketing structure shared with Signia Hilton Bonnet Creek</t>
         </is>
       </c>
+      <c r="J167" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -37082,6 +38457,11 @@
           <t>4510 W. Vine St., Kissimmee -- medievaltimes.com/orlando</t>
         </is>
       </c>
+      <c r="J168" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -37119,6 +38499,11 @@
           <t>piratesdinneradventure.com -- 6400 Carrier Dr, Orlando</t>
         </is>
       </c>
+      <c r="J169" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -37156,6 +38541,11 @@
           <t>theescapegame.com/orlando</t>
         </is>
       </c>
+      <c r="J170" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -37193,6 +38583,11 @@
           <t>8986 International Dr -- national brand with local activation budget</t>
         </is>
       </c>
+      <c r="J171" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -37230,6 +38625,11 @@
           <t>ripleys.com -- 8201 International Dr</t>
         </is>
       </c>
+      <c r="J172" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -37267,6 +38667,11 @@
           <t>iconparkorlando.com/strategic-partnerships-2 -- multiple venues under one umbrella</t>
         </is>
       </c>
+      <c r="J173" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -37304,6 +38709,11 @@
           <t>sf3.sugarfactory.com/orlando-fl -- inside ICON Park</t>
         </is>
       </c>
+      <c r="J174" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -37341,6 +38751,11 @@
           <t>mistercarwash.com -- corporate HQ Tucson; regional marketing contact</t>
         </is>
       </c>
+      <c r="J175" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -37378,6 +38793,11 @@
           <t>corporate.sunrail.com -- info@sunrail.com</t>
         </is>
       </c>
+      <c r="J176" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -37415,6 +38835,11 @@
           <t>gobrightline.com/press-room -- aggressive partnership expansion 2025-2026</t>
         </is>
       </c>
+      <c r="J177" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -37452,6 +38877,11 @@
           <t>worldfoodtrucks.com -- 5811 W Irlo Bronson Memorial Hwy, Kissimmee</t>
         </is>
       </c>
+      <c r="J178" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -37489,6 +38919,11 @@
           <t>fun-spot.com -- family-owned, decision-maker accessible</t>
         </is>
       </c>
+      <c r="J179" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -37526,6 +38961,11 @@
           <t>viewclermont.com -- 2601 Clermont National Dr, Clermont FL</t>
         </is>
       </c>
+      <c r="J180" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -37563,6 +39003,11 @@
           <t>501 W. Church St., Downtown Orlando -- travelandleisureco.com</t>
         </is>
       </c>
+      <c r="J181" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -37600,6 +39045,11 @@
           <t>christmasatgaylordpalms.com -- 6000 W Osceola Pkwy, Kissimmee</t>
         </is>
       </c>
+      <c r="J182" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -37637,6 +39087,11 @@
           <t>curlmix.com -- Black-owned Chicago brand, Ulta</t>
         </is>
       </c>
+      <c r="J183" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -37674,6 +39129,11 @@
           <t>breadbeautysupply.com</t>
         </is>
       </c>
+      <c r="J184" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -37711,6 +39171,11 @@
           <t>patternbeauty.com -- Ulta, Sephora, Target</t>
         </is>
       </c>
+      <c r="J185" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -37748,6 +39213,11 @@
           <t>cecred.com -- Ulta</t>
         </is>
       </c>
+      <c r="J186" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -37785,6 +39255,11 @@
           <t>camillerosenaturals.com -- Ulta, Target, Walmart</t>
         </is>
       </c>
+      <c r="J187" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -37822,6 +39297,11 @@
           <t>adwoabeauty.com -- Sephora</t>
         </is>
       </c>
+      <c r="J188" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -37859,6 +39339,11 @@
           <t>briogeohair.com -- Ulta, Sephora</t>
         </is>
       </c>
+      <c r="J189" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -37896,6 +39381,11 @@
           <t>bigbudpress.com -- LA based, ships nationally</t>
         </is>
       </c>
+      <c r="J190" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -37933,6 +39423,11 @@
           <t>wildfang.com</t>
         </is>
       </c>
+      <c r="J191" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -37970,6 +39465,11 @@
           <t>littlewordsproject.com -- actively seeks nano/micro gifting</t>
         </is>
       </c>
+      <c r="J192" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -38007,6 +39507,11 @@
           <t>mixbar.com</t>
         </is>
       </c>
+      <c r="J193" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -38044,6 +39549,11 @@
           <t>princesspolly.com</t>
         </is>
       </c>
+      <c r="J194" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -38081,6 +39591,11 @@
           <t>kissusa.com / impressbeauty.com</t>
         </is>
       </c>
+      <c r="J195" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -38118,6 +39633,11 @@
           <t>redaspenlove.com</t>
         </is>
       </c>
+      <c r="J196" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -38155,6 +39675,11 @@
           <t>erincondren.com -- active ambassador program</t>
         </is>
       </c>
+      <c r="J197" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -38187,6 +39712,11 @@
           <t>Near Orlando Public Library -- new opening, great 'discover local' content</t>
         </is>
       </c>
+      <c r="J198" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -38222,6 +39752,11 @@
       <c r="H199" t="inlineStr">
         <is>
           <t>level99.com -- new opening Orlando</t>
+        </is>
+      </c>
+      <c r="J199" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
         </is>
       </c>
     </row>
@@ -38236,7 +39771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -38250,6 +39785,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38308,6 +39844,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="L1" s="31" t="inlineStr">
+        <is>
+          <t>Research Needed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
@@ -38361,6 +39902,11 @@
         </is>
       </c>
       <c r="K2" s="30" t="inlineStr"/>
+      <c r="L2" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38413,6 +39959,11 @@
           <t>Not Contacted</t>
         </is>
       </c>
+      <c r="L3" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
@@ -38466,6 +40017,11 @@
         </is>
       </c>
       <c r="K4" s="30" t="inlineStr"/>
+      <c r="L4" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38523,6 +40079,11 @@
           <t>Author of 'Professional Troublemaker'</t>
         </is>
       </c>
+      <c r="L5" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="30" t="inlineStr">
@@ -38580,6 +40141,11 @@
           <t>More editorial, harder to pitch</t>
         </is>
       </c>
+      <c r="L6" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38637,6 +40203,11 @@
           <t>More commentary format, limited guest slots</t>
         </is>
       </c>
+      <c r="L7" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
@@ -38690,6 +40261,11 @@
         </is>
       </c>
       <c r="K8" s="30" t="inlineStr"/>
+      <c r="L8" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38742,6 +40318,11 @@
           <t>Not Contacted</t>
         </is>
       </c>
+      <c r="L9" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
@@ -38795,6 +40376,11 @@
         </is>
       </c>
       <c r="K10" s="30" t="inlineStr"/>
+      <c r="L10" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -38852,6 +40438,11 @@
           <t>OWN Network podcast</t>
         </is>
       </c>
+      <c r="L11" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="30" t="inlineStr">
@@ -38909,6 +40500,11 @@
           <t>THE body politics podcast -- academic + cultural. Danni's medical training work is exact fit</t>
         </is>
       </c>
+      <c r="L12" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -38966,6 +40562,11 @@
           <t>Direct body image podcast -- submit at shesallfat.com</t>
         </is>
       </c>
+      <c r="L13" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -39023,6 +40624,11 @@
           <t>Anti-diet dietitian; IBI co-creator angle is the hook</t>
         </is>
       </c>
+      <c r="L14" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39075,6 +40681,11 @@
           <t>Not Contacted</t>
         </is>
       </c>
+      <c r="L15" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
@@ -39128,6 +40739,11 @@
         </is>
       </c>
       <c r="K16" s="30" t="inlineStr"/>
+      <c r="L16" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39185,6 +40801,11 @@
           <t>Fat liberation podcast</t>
         </is>
       </c>
+      <c r="L17" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
@@ -39242,6 +40863,11 @@
           <t>Sonya Renee Taylor's show</t>
         </is>
       </c>
+      <c r="L18" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39294,6 +40920,11 @@
           <t>Not Contacted</t>
         </is>
       </c>
+      <c r="L19" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
@@ -39351,6 +40982,11 @@
           <t>Influencer marketing podcast</t>
         </is>
       </c>
+      <c r="L20" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -39403,6 +41039,11 @@
           <t>Not Contacted</t>
         </is>
       </c>
+      <c r="L21" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
@@ -39456,6 +41097,11 @@
         </is>
       </c>
       <c r="K22" s="30" t="inlineStr"/>
+      <c r="L22" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -39513,6 +41159,11 @@
           <t>Harder to get booked, high payoff</t>
         </is>
       </c>
+      <c r="L23" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
@@ -39566,6 +41217,11 @@
         </is>
       </c>
       <c r="K24" s="30" t="inlineStr"/>
+      <c r="L24" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -39623,6 +41279,11 @@
           <t>UK-based but global audience</t>
         </is>
       </c>
+      <c r="L25" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
@@ -39680,6 +41341,11 @@
           <t>Short story format -- pitch as a mini feature</t>
         </is>
       </c>
+      <c r="L26" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -39737,6 +41403,11 @@
           <t>Glennon is Florida-based (Naples) -- local angle possible</t>
         </is>
       </c>
+      <c r="L27" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
@@ -39794,6 +41465,11 @@
           <t>Harvard Law -- Harvard connection could be a hook</t>
         </is>
       </c>
+      <c r="L28" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -39846,6 +41522,11 @@
           <t>Not Contacted</t>
         </is>
       </c>
+      <c r="L29" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
@@ -39903,6 +41584,11 @@
           <t>Harder to get booked; very selective</t>
         </is>
       </c>
+      <c r="L30" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -39955,6 +41641,11 @@
           <t>Not Contacted</t>
         </is>
       </c>
+      <c r="L31" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
@@ -40012,6 +41703,11 @@
           <t>Soledad O'Brien is a journalist, so NPR/Vogue credentials matter</t>
         </is>
       </c>
+      <c r="L32" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -40069,6 +41765,11 @@
           <t>Youth empowerment focus -- shelter/mentoring work is the hook</t>
         </is>
       </c>
+      <c r="L33" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="30" t="inlineStr">
@@ -40126,6 +41827,11 @@
           <t>Miami-based; drive or fly for in-person</t>
         </is>
       </c>
+      <c r="L34" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -40183,6 +41889,11 @@
           <t>NYC studio; need strong news hook to get booked</t>
         </is>
       </c>
+      <c r="L35" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="30" t="inlineStr">
@@ -40240,6 +41951,11 @@
           <t>Atlanta -- in-person possible (drive from Orlando)</t>
         </is>
       </c>
+      <c r="L36" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -40297,6 +42013,11 @@
           <t>Local visibility, easy win for community building</t>
         </is>
       </c>
+      <c r="L37" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="30" t="inlineStr">
@@ -40354,6 +42075,11 @@
           <t>Local Orlando TV stations with podcast extensions</t>
         </is>
       </c>
+      <c r="L38" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -40411,6 +42137,11 @@
           <t>Atlanta -- in-person possible</t>
         </is>
       </c>
+      <c r="L39" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="30" t="inlineStr">
@@ -40468,6 +42199,11 @@
           <t>HBCU audience = direct pipeline to campus speaking gigs</t>
         </is>
       </c>
+      <c r="L40" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -40525,6 +42261,11 @@
           <t>Industry podcast for speakers -- credibility building + direct client pipeline</t>
         </is>
       </c>
+      <c r="L41" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="30" t="inlineStr">
@@ -40578,6 +42319,11 @@
         </is>
       </c>
       <c r="K42" s="30" t="inlineStr"/>
+      <c r="L42" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -40635,6 +42381,11 @@
           <t>Niche but direct pipeline to booking opportunities</t>
         </is>
       </c>
+      <c r="L43" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="30" t="inlineStr">
@@ -40692,6 +42443,11 @@
           <t>Hard to get booked; need strong health angle</t>
         </is>
       </c>
+      <c r="L44" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -40749,6 +42505,11 @@
           <t>Health equity podcast -- IBI co-creator is the perfect hook</t>
         </is>
       </c>
+      <c r="L45" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="30" t="inlineStr">
@@ -40804,6 +42565,11 @@
       <c r="K46" s="30" t="inlineStr">
         <is>
           <t>UK-based but global reach; IBI work is the hook</t>
+        </is>
+      </c>
+      <c r="L46" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
         </is>
       </c>
     </row>
@@ -40818,7 +42584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -40831,6 +42597,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40884,6 +42651,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="K1" s="31" t="inlineStr">
+        <is>
+          <t>Research Needed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
@@ -40932,6 +42704,11 @@
           <t>Orange County Convention Center -- 1,100+ exhibitors. She is LOCAL Orlando talent.</t>
         </is>
       </c>
+      <c r="K2" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40979,6 +42756,11 @@
           <t>Already passed June 2026 -- note for SHRM 2027</t>
         </is>
       </c>
+      <c r="K3" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
@@ -41027,6 +42809,11 @@
           <t>Institute for Body Image is the hook -- training medical professionals</t>
         </is>
       </c>
+      <c r="K4" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41074,6 +42861,11 @@
           <t>christmasatgaylordpalms.com -- influencer/media partnership potential</t>
         </is>
       </c>
+      <c r="K5" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="30" t="inlineStr">
@@ -41122,6 +42914,11 @@
           <t>Free community event -- visibility + community credibility</t>
         </is>
       </c>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41169,6 +42966,11 @@
           <t>Atlanta -- 5.5hr drive</t>
         </is>
       </c>
+      <c r="K7" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
@@ -41217,6 +43019,11 @@
           <t>Atlanta -- her MPA gives her credibility in this room</t>
         </is>
       </c>
+      <c r="K8" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41264,6 +43071,11 @@
           <t>She fits the entrepreneurship track -- Harvard + no agent + brand deals</t>
         </is>
       </c>
+      <c r="K9" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
@@ -41312,6 +43124,11 @@
           <t>National Association of Black Journalists -- NPR + Vogue + media credentials are the hook</t>
         </is>
       </c>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41359,6 +43176,11 @@
           <t>Professional development audience -- resilience + community building talk</t>
         </is>
       </c>
+      <c r="K11" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="30" t="inlineStr">
@@ -41407,6 +43229,11 @@
           <t>THE event. Competitive to get into -- needs strong pitch and timing. Fly or drive.</t>
         </is>
       </c>
+      <c r="K12" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41454,6 +43281,11 @@
           <t>Local Orlando -- anchor event for women professionals</t>
         </is>
       </c>
+      <c r="K13" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -41502,6 +43334,11 @@
           <t>NPR + Jennifer Hudson + Tamron + TLC are the credentials</t>
         </is>
       </c>
+      <c r="K14" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41549,6 +43386,11 @@
           <t>Social media + creator space -- 4% engagement is the hook</t>
         </is>
       </c>
+      <c r="K15" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
@@ -41597,6 +43439,11 @@
           <t>Creator/entrepreneur event -- 'nobody is coming to save you' is made for this stage</t>
         </is>
       </c>
+      <c r="K16" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41644,6 +43491,11 @@
           <t>Industry conference -- credibility builder for brand side</t>
         </is>
       </c>
+      <c r="K17" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
@@ -41692,6 +43544,11 @@
           <t>Already in her speaking resume (Seminole Leadership). Ask for state-level invite.</t>
         </is>
       </c>
+      <c r="K18" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41739,6 +43596,11 @@
           <t>Natural audience -- Black youth leadership</t>
         </is>
       </c>
+      <c r="K19" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
@@ -41783,6 +43645,11 @@
         </is>
       </c>
       <c r="J20" s="30" t="inlineStr"/>
+      <c r="K20" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -41828,6 +43695,11 @@
       <c r="J21" t="inlineStr">
         <is>
           <t>She already does this work at shelters and mentoring programs</t>
+        </is>
+      </c>
+      <c r="K21" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
         </is>
       </c>
     </row>

--- a/danni_adams_outreach_tracker.xlsx
+++ b/danni_adams_outreach_tracker.xlsx
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5148,6 +5148,614 @@
       <c r="L97" s="33" t="inlineStr">
         <is>
           <t>Email needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>UCF Dept of Sociology</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Dr. Jason Ford, Chair</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Jason.Ford@ucf.edu</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Public Admin / Sociology dept. Media literacy, identity, storytelling pitch. FSU sociology BA hook.</t>
+        </is>
+      </c>
+      <c r="L98" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>UCF Nicholson School of Communication &amp; Media</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>nassc@ucf.edu</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Dr. Nan Yu, Interim Director</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Nan.Yu@ucf.edu</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Communications school at UCF -- home court. Perfect for media literacy + social media talk.</t>
+        </is>
+      </c>
+      <c r="L99" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>UF Dept of Sociology &amp; Criminology</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Gainesville, FL</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Dr. Stephen Perz, Chair</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>sperz@ufl.edu</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>UF sociology dept. Representation, media, identity topics. BA Sociology hook.</t>
+        </is>
+      </c>
+      <c r="L100" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>USF Dept of Communication</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Dr. Steve Wilson, Chair</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>wilson52@usf.edu</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>USF Communication dept. Storytelling, media literacy, social media angle.</t>
+        </is>
+      </c>
+      <c r="L101" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Florida A&amp;M University -- Student Activities</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Cateatra Mallard, Director of Student Union &amp; Activities</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>cateatra.mallard@famu.edu</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>HBCU -- all-campus programming. Representation, identity, resilience talk. Strong fit.</t>
+        </is>
+      </c>
+      <c r="L102" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FIU School of Communication (CARTA)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Jessica Delgado, Dept Chair</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>delgadoj@fiu.edu</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>FIU CARTA -- large diverse student body. Media literacy + social media perfect fit.</t>
+        </is>
+      </c>
+      <c r="L103" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Boys &amp; Girls Clubs of Southeast Georgia</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Brunswick, GA</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>bgcglynn@gmail.com</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>TJ Andrews, Director of Operations</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>tj@bgcsega.com</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>BGC ALUMNI PITCH -- open with: I grew up in your clubs. Perseverance / resilience talk.</t>
+        </is>
+      </c>
+      <c r="L104" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Boys &amp; Girls Clubs of Broward County</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Felix Collazo, Sr. Director of Program Strategy &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>fcollazo@bgcbc.org</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>BGC ALUMNI PITCH -- she grew up in BGC. Collazo runs programming. CEO: cgentile@bgcbc.org.</t>
+        </is>
+      </c>
+      <c r="L105" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Jack and Jill of America, Inc.</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>(202) 667-7010</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>info@jack-and-jill.org</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>info@jack-and-jill.org</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Call (202) 667-7010 first to get programming contact name before emailing HQ inbox.</t>
+        </is>
+      </c>
+      <c r="L106" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Alpha Kappa Alpha Sorority, Inc.</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>International Communications Committee</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AKAChampioncomms@aka1908.com</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Handles keynote and appearance requests per their site. Warm chapter intro beats cold national pitch.</t>
+        </is>
+      </c>
+      <c r="L107" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Delta Sigma Theta Sorority, Inc.</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Program Planning &amp; Development</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>programsupport@dstinc.org</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Use programsupport@ for speaking pitches. Chapter-level intro is warmer path than national cold.</t>
+        </is>
+      </c>
+      <c r="L108" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>National Urban League</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Teresa Candori, Conference/Media Contact</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>tcandori@nul.org</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Pitch 2027 NUL programming now. Community building, civic engagement, storytelling angle.</t>
+        </is>
+      </c>
+      <c r="L109" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>National Coalition of 100 Black Women</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>(404) 390-3982</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>contactus@nc100bw.org</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>contactus@nc100bw.org</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>NCBW -- leadership, representation, body image advocacy directly in their lane.</t>
+        </is>
+      </c>
+      <c r="L110" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Girl Talk Foundation</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Denetria D. Moore, Executive Director</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>denetria@girltalkinc.com</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Girls mentoring org -- perseverance, confidence, dreaming big. Also: Maya Brown (Program Dir): maya@girltalkinc.com</t>
+        </is>
+      </c>
+      <c r="L111" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
     </row>
@@ -30326,7 +30934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J199"/>
+  <dimension ref="A1:J211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -39755,6 +40363,600 @@
         </is>
       </c>
       <c r="J199" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Juvia's Place</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Black-Owned Beauty / Eyeshadow</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Black-owned, vibrant celebration of Blackness -- her audience is their audience.</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Affiliates / Press Contact</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>affiliates@juviasplace.com</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>@juviasplace</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Also try press@juviasplace.com for press angle.</t>
+        </is>
+      </c>
+      <c r="J200" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Mielle Organics</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Natural Hair Care (P&amp;G)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Natural hair care, Black women audience. Now a P&amp;G brand -- larger budget.</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>PR / Media</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>pr@mielleorganics.com</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>@mielleorganics</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Confirmed email from PR directories. P&amp;G acquisition = larger partnership budget.</t>
+        </is>
+      </c>
+      <c r="J201" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SheaMoisture</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Natural Hair &amp; Skin (Unilever)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Black women, natural hair, self-care -- core audience overlap. Unilever brand = real budget.</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Influencer Contact (via Influential agency)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>sheamoisture@influential.co</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>@sheamoisture</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Confirmed from Unilever USA official media contacts. Goes to Influential agency.</t>
+        </is>
+      </c>
+      <c r="J202" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Cantu Beauty</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Natural Hair Care</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Natural hair, textured hair, Black women core audience.</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PR Agency -- Reddish PR, Brianna Cameron</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>bcameron@reddishpr.com</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>@cantubeauty</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Brianna Cameron at Reddish PR handles Cantu. Confirm still current before sending.</t>
+        </is>
+      </c>
+      <c r="J203" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Carol's Daughter</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Natural Hair &amp; Skin (LOreal)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Natural hair, Black women heritage brand. LOreal ownership = real influencer budget.</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Press / Influencer Contact</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>press@support.carolsdaughter.com</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>@carolsdaughter</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Also look up Amiya McCargo (Social/Influencer team) on LinkedIn.</t>
+        </is>
+      </c>
+      <c r="J204" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Rebdolls</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Plus-size, body positive, Black women centered -- exact audience match.</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Influencer &amp; Press</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>influencers@rebdolls.com</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>@rebdolls</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Confirmed from official rebdolls.com contact page. Also: press@rebdolls.com.</t>
+        </is>
+      </c>
+      <c r="J205" s="32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Torrid</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Largest plus-size specialty retailer in the US. Massive audience overlap.</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Influencer Marketing Manager (LinkedIn)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>@torrid</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>No public pitch email. Find IM Manager on LinkedIn. Email format: first.last@torrid.com</t>
+        </is>
+      </c>
+      <c r="J206" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Lane Bryant</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Iconic plus-size brand, core audience match.</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Influencer Marketing Manager (LinkedIn)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>@lanebryant</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>PR via Coyne PR agency. Find IM Manager on LinkedIn. Format: FLast@lanebryant.com</t>
+        </is>
+      </c>
+      <c r="J207" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Ashley Stewart</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Plus-size, Black women focused heritage brand.</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Influencer Marketing Manager (LinkedIn)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>@ashleystewart</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>No public email. LinkedIn: Influencer Marketing Manager at Ashley Stewart. Format: FLast@ashleystewart.com</t>
+        </is>
+      </c>
+      <c r="J208" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Fenty Beauty</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Beauty (LVMH)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Rihanna brand -- inclusivity, diversity, exactly her world.</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Instagram DM or LVMH PR</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>@fentybeauty</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>No public influencer email (high scam risk on fake ones). Approach via Instagram DM or LVMH press office.</t>
+        </is>
+      </c>
+      <c r="J209" s="33" t="inlineStr">
+        <is>
+          <t>Email needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Eloquii</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Plus-Size Fashion (WHP Global)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>PAST PARTNER -- reactivate existing relationship, not cold outreach.</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Existing Relationship -- reactivate</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>@eloquii</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>PAST PARTNER. Find current IM Manager on LinkedIn. Do not cold pitch -- reference prior partnership.</t>
+        </is>
+      </c>
+      <c r="J210" s="34" t="inlineStr">
+        <is>
+          <t>Review: no direct email</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Universal Standard</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Inclusive Fashion</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Size-inclusive fashion, premium, body image mission alignment.</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Affiliate / Partnerships (Lab6 Media)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>@universalstandard</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Apply at universalstandard.com/pages/affiliate-sign-up-page. Agency: Lab6 Media.</t>
+        </is>
+      </c>
+      <c r="J211" s="33" t="inlineStr">
         <is>
           <t>Email needed</t>
         </is>
